--- a/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
+++ b/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2939F8A-9AA0-43B5-9CA2-E5E0B9417286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC487830-2BCE-47FB-B336-8AE94D55A3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3094" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3124" uniqueCount="661">
   <si>
     <t>HONDA 62XS CONTAINER</t>
   </si>
@@ -3463,6 +3463,18 @@
   </si>
   <si>
     <t>6WZX - MP0 event</t>
+  </si>
+  <si>
+    <t>37820-6WZ-M61</t>
+  </si>
+  <si>
+    <t>37820-6WZ-M71</t>
+  </si>
+  <si>
+    <t>https://rb-pde-int.bosch.com:8881/app/ShowJob/16406</t>
+  </si>
+  <si>
+    <t>WF16408</t>
   </si>
 </sst>
 </file>
@@ -18150,10 +18162,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J23," ",""),"-","")</f>
         <v>3782062XMD10M6</v>
       </c>
-      <c r="AN23" s="51" t="s">
+      <c r="AN23" s="77" t="s">
         <v>249</v>
       </c>
-      <c r="AO23" s="51" t="s">
+      <c r="AO23" s="77" t="s">
         <v>416</v>
       </c>
       <c r="AP23" s="51" t="s">
@@ -18180,7 +18192,7 @@
       <c r="AV23" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW23" s="80" t="s">
+      <c r="AW23" s="77" t="s">
         <v>517</v>
       </c>
       <c r="AX23" s="54" t="str">
@@ -19130,10 +19142,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J26," ",""),"-","")</f>
         <v>3782062XME10M6</v>
       </c>
-      <c r="AN26" s="51" t="s">
+      <c r="AN26" s="77" t="s">
         <v>411</v>
       </c>
-      <c r="AO26" s="51" t="s">
+      <c r="AO26" s="77" t="s">
         <v>417</v>
       </c>
       <c r="AP26" s="51" t="s">
@@ -19160,7 +19172,7 @@
       <c r="AV26" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW26" s="80" t="s">
+      <c r="AW26" s="77" t="s">
         <v>518</v>
       </c>
       <c r="AX26" s="54" t="str">
@@ -20110,10 +20122,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J29," ",""),"-","")</f>
         <v>3782062XMF10M6</v>
       </c>
-      <c r="AN29" s="51" t="s">
+      <c r="AN29" s="77" t="s">
         <v>412</v>
       </c>
-      <c r="AO29" s="51" t="s">
+      <c r="AO29" s="77" t="s">
         <v>418</v>
       </c>
       <c r="AP29" s="51" t="s">
@@ -20140,7 +20152,7 @@
       <c r="AV29" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW29" s="80" t="s">
+      <c r="AW29" s="77" t="s">
         <v>520</v>
       </c>
       <c r="AX29" s="54" t="str">
@@ -21090,10 +21102,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J32," ",""),"-","")</f>
         <v>3782062XMG10M6</v>
       </c>
-      <c r="AN32" s="51" t="s">
+      <c r="AN32" s="77" t="s">
         <v>415</v>
       </c>
-      <c r="AO32" s="51" t="s">
+      <c r="AO32" s="77" t="s">
         <v>419</v>
       </c>
       <c r="AP32" s="51" t="s">
@@ -21120,7 +21132,7 @@
       <c r="AV32" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW32" s="80" t="s">
+      <c r="AW32" s="77" t="s">
         <v>522</v>
       </c>
       <c r="AX32" s="54" t="str">
@@ -22070,10 +22082,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J35," ",""),"-","")</f>
         <v>3782062XMH10M6</v>
       </c>
-      <c r="AN35" s="51" t="s">
+      <c r="AN35" s="77" t="s">
         <v>414</v>
       </c>
-      <c r="AO35" s="51" t="s">
+      <c r="AO35" s="77" t="s">
         <v>420</v>
       </c>
       <c r="AP35" s="51" t="s">
@@ -22100,7 +22112,7 @@
       <c r="AV35" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW35" s="80" t="s">
+      <c r="AW35" s="77" t="s">
         <v>519</v>
       </c>
       <c r="AX35" s="54" t="str">
@@ -23050,10 +23062,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J38," ",""),"-","")</f>
         <v>3782062XMJ10M6</v>
       </c>
-      <c r="AN38" s="51" t="s">
+      <c r="AN38" s="77" t="s">
         <v>413</v>
       </c>
-      <c r="AO38" s="51" t="s">
+      <c r="AO38" s="77" t="s">
         <v>421</v>
       </c>
       <c r="AP38" s="51" t="s">
@@ -23080,7 +23092,7 @@
       <c r="AV38" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW38" s="80" t="s">
+      <c r="AW38" s="77" t="s">
         <v>521</v>
       </c>
       <c r="AX38" s="54" t="str">
@@ -24030,10 +24042,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J41," ",""),"-","")</f>
         <v>3782062XMD20M6</v>
       </c>
-      <c r="AN41" s="51" t="s">
+      <c r="AN41" s="77" t="s">
         <v>555</v>
       </c>
-      <c r="AO41" s="51" t="s">
+      <c r="AO41" s="77" t="s">
         <v>573</v>
       </c>
       <c r="AP41" s="51" t="s">
@@ -24060,7 +24072,7 @@
       <c r="AV41" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW41" s="80" t="s">
+      <c r="AW41" s="77" t="s">
         <v>627</v>
       </c>
       <c r="AX41" s="54" t="str">
@@ -25008,10 +25020,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J44," ",""),"-","")</f>
         <v>3782062XME20M6</v>
       </c>
-      <c r="AN44" s="51" t="s">
+      <c r="AN44" s="77" t="s">
         <v>556</v>
       </c>
-      <c r="AO44" s="51" t="s">
+      <c r="AO44" s="77" t="s">
         <v>574</v>
       </c>
       <c r="AP44" s="51" t="s">
@@ -25038,7 +25050,7 @@
       <c r="AV44" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW44" s="80" t="s">
+      <c r="AW44" s="77" t="s">
         <v>628</v>
       </c>
       <c r="AX44" s="54" t="str">
@@ -25986,10 +25998,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J47," ",""),"-","")</f>
         <v>3782062XMF20M6</v>
       </c>
-      <c r="AN47" s="51" t="s">
+      <c r="AN47" s="77" t="s">
         <v>557</v>
       </c>
-      <c r="AO47" s="51" t="s">
+      <c r="AO47" s="77" t="s">
         <v>575</v>
       </c>
       <c r="AP47" s="51" t="s">
@@ -26016,7 +26028,7 @@
       <c r="AV47" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW47" s="80" t="s">
+      <c r="AW47" s="77" t="s">
         <v>629</v>
       </c>
       <c r="AX47" s="54" t="str">
@@ -26964,10 +26976,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J50," ",""),"-","")</f>
         <v>3782062XMG20M6</v>
       </c>
-      <c r="AN50" s="51" t="s">
+      <c r="AN50" s="77" t="s">
         <v>558</v>
       </c>
-      <c r="AO50" s="51" t="s">
+      <c r="AO50" s="77" t="s">
         <v>576</v>
       </c>
       <c r="AP50" s="51" t="s">
@@ -26994,7 +27006,7 @@
       <c r="AV50" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW50" s="80" t="s">
+      <c r="AW50" s="77" t="s">
         <v>630</v>
       </c>
       <c r="AX50" s="54" t="str">
@@ -27942,10 +27954,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J53," ",""),"-","")</f>
         <v>3782062XMH20M6</v>
       </c>
-      <c r="AN53" s="51" t="s">
+      <c r="AN53" s="77" t="s">
         <v>559</v>
       </c>
-      <c r="AO53" s="51" t="s">
+      <c r="AO53" s="77" t="s">
         <v>577</v>
       </c>
       <c r="AP53" s="51" t="s">
@@ -27972,7 +27984,7 @@
       <c r="AV53" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW53" s="80" t="s">
+      <c r="AW53" s="77" t="s">
         <v>631</v>
       </c>
       <c r="AX53" s="54" t="str">
@@ -28920,10 +28932,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J56," ",""),"-","")</f>
         <v>3782062XMJ20M6</v>
       </c>
-      <c r="AN56" s="51" t="s">
+      <c r="AN56" s="77" t="s">
         <v>560</v>
       </c>
-      <c r="AO56" s="51" t="s">
+      <c r="AO56" s="77" t="s">
         <v>578</v>
       </c>
       <c r="AP56" s="51" t="s">
@@ -28950,7 +28962,7 @@
       <c r="AV56" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW56" s="80" t="s">
+      <c r="AW56" s="77" t="s">
         <v>632</v>
       </c>
       <c r="AX56" s="54" t="str">
@@ -29797,7 +29809,9 @@
       <c r="H59" s="51" t="s">
         <v>656</v>
       </c>
-      <c r="I59" s="78"/>
+      <c r="I59" s="78" t="s">
+        <v>659</v>
+      </c>
       <c r="J59" s="53" t="s">
         <v>644</v>
       </c>
@@ -29819,18 +29833,36 @@
       <c r="S59" s="51" t="s">
         <v>404</v>
       </c>
-      <c r="T59" s="51"/>
-      <c r="U59" s="51"/>
-      <c r="V59" s="51"/>
-      <c r="W59" s="51"/>
-      <c r="X59" s="51"/>
-      <c r="Y59" s="51"/>
-      <c r="Z59" s="51"/>
-      <c r="AA59" s="51"/>
+      <c r="T59" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="U59" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="V59" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="W59" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="X59" s="51" t="s">
+        <v>405</v>
+      </c>
+      <c r="Y59" s="51" t="s">
+        <v>405</v>
+      </c>
+      <c r="Z59" s="51" t="s">
+        <v>405</v>
+      </c>
+      <c r="AA59" s="51" t="s">
+        <v>405</v>
+      </c>
       <c r="AB59" s="51" t="s">
         <v>648</v>
       </c>
-      <c r="AC59" s="51"/>
+      <c r="AC59" s="51">
+        <v>93</v>
+      </c>
       <c r="AD59" s="51" t="s">
         <v>407</v>
       </c>
@@ -29840,7 +29872,9 @@
       <c r="AF59" s="51" t="s">
         <v>649</v>
       </c>
-      <c r="AG59" s="51"/>
+      <c r="AG59" s="51" t="s">
+        <v>389</v>
+      </c>
       <c r="AH59" s="51" t="s">
         <v>38</v>
       </c>
@@ -29860,7 +29894,9 @@
       </c>
       <c r="AN59" s="51"/>
       <c r="AO59" s="51"/>
-      <c r="AP59" s="51"/>
+      <c r="AP59" s="51" t="s">
+        <v>404</v>
+      </c>
       <c r="AQ59" s="54" t="str">
         <f>SUBSTITUTE(J59," ","")</f>
         <v>37820-6WZ-M610-M6</v>
@@ -29877,7 +29913,9 @@
       <c r="AU59" s="51" t="s">
         <v>422</v>
       </c>
-      <c r="AV59" s="51"/>
+      <c r="AV59" s="51" t="s">
+        <v>423</v>
+      </c>
       <c r="AW59" s="80"/>
       <c r="AX59" s="54">
         <f>K59</f>
@@ -29887,10 +29925,12 @@
       <c r="AZ59" s="51"/>
       <c r="BA59" s="51"/>
       <c r="BB59" s="51"/>
-      <c r="BC59" s="51"/>
-      <c r="BD59" s="54">
+      <c r="BC59" s="51" t="s">
+        <v>425</v>
+      </c>
+      <c r="BD59" s="54" t="str">
         <f>AP59</f>
-        <v>0</v>
+        <v>MG1CS022</v>
       </c>
       <c r="BE59" s="51" t="s">
         <v>648</v>
@@ -29898,7 +29938,9 @@
       <c r="BF59" s="51" t="s">
         <v>542</v>
       </c>
-      <c r="BG59" s="51"/>
+      <c r="BG59" s="51" t="s">
+        <v>467</v>
+      </c>
       <c r="BH59" s="51" t="s">
         <v>428</v>
       </c>
@@ -30051,7 +30093,9 @@
         <v>645</v>
       </c>
       <c r="CW59" s="81"/>
-      <c r="CX59" s="51"/>
+      <c r="CX59" s="51" t="s">
+        <v>657</v>
+      </c>
       <c r="CY59" s="51" t="s">
         <v>647</v>
       </c>
@@ -30308,35 +30352,35 @@
       <c r="S61" s="47"/>
       <c r="T61" s="47" t="b">
         <f>T59=T60</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U61" s="47" t="b">
         <f t="shared" ref="U61:AZ61" si="350">U59=U60</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB61" s="47" t="b">
         <f t="shared" si="350"/>
@@ -30344,7 +30388,7 @@
       </c>
       <c r="AC61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD61" s="47" t="b">
         <f t="shared" si="350"/>
@@ -30360,7 +30404,7 @@
       </c>
       <c r="AG61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH61" s="47" t="b">
         <f t="shared" si="350"/>
@@ -30396,7 +30440,7 @@
       </c>
       <c r="AP61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ61" s="47" t="b">
         <f t="shared" si="350"/>
@@ -30420,7 +30464,7 @@
       </c>
       <c r="AV61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW61" s="47" t="b">
         <f t="shared" si="350"/>
@@ -30446,11 +30490,11 @@
       </c>
       <c r="BC61" s="47" t="b">
         <f t="shared" ref="BC61:BH61" si="351">BC59=BC60</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD61" s="47" t="b">
         <f t="shared" si="351"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE61" s="47" t="b">
         <f t="shared" si="351"/>
@@ -30462,7 +30506,7 @@
       </c>
       <c r="BG61" s="47" t="b">
         <f t="shared" si="351"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH61" s="47" t="b">
         <f t="shared" si="351"/>
@@ -30623,7 +30667,9 @@
       <c r="H62" s="51" t="s">
         <v>656</v>
       </c>
-      <c r="I62" s="78"/>
+      <c r="I62" s="78" t="s">
+        <v>660</v>
+      </c>
       <c r="J62" s="53" t="s">
         <v>652</v>
       </c>
@@ -30645,18 +30691,36 @@
       <c r="S62" s="51" t="s">
         <v>404</v>
       </c>
-      <c r="T62" s="51"/>
-      <c r="U62" s="51"/>
-      <c r="V62" s="51"/>
-      <c r="W62" s="51"/>
-      <c r="X62" s="51"/>
-      <c r="Y62" s="51"/>
-      <c r="Z62" s="51"/>
-      <c r="AA62" s="51"/>
+      <c r="T62" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="U62" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="V62" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="W62" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="X62" s="51" t="s">
+        <v>405</v>
+      </c>
+      <c r="Y62" s="51" t="s">
+        <v>405</v>
+      </c>
+      <c r="Z62" s="51" t="s">
+        <v>405</v>
+      </c>
+      <c r="AA62" s="51" t="s">
+        <v>405</v>
+      </c>
       <c r="AB62" s="51" t="s">
         <v>648</v>
       </c>
-      <c r="AC62" s="51"/>
+      <c r="AC62" s="51">
+        <v>93</v>
+      </c>
       <c r="AD62" s="51" t="s">
         <v>407</v>
       </c>
@@ -30666,7 +30730,9 @@
       <c r="AF62" s="51" t="s">
         <v>649</v>
       </c>
-      <c r="AG62" s="51"/>
+      <c r="AG62" s="51" t="s">
+        <v>389</v>
+      </c>
       <c r="AH62" s="51" t="s">
         <v>38</v>
       </c>
@@ -30686,7 +30752,9 @@
       </c>
       <c r="AN62" s="51"/>
       <c r="AO62" s="51"/>
-      <c r="AP62" s="51"/>
+      <c r="AP62" s="51" t="s">
+        <v>404</v>
+      </c>
       <c r="AQ62" s="54" t="str">
         <f>SUBSTITUTE(J62," ","")</f>
         <v>37820-6WZ-M710-M6</v>
@@ -30703,7 +30771,9 @@
       <c r="AU62" s="51" t="s">
         <v>422</v>
       </c>
-      <c r="AV62" s="51"/>
+      <c r="AV62" s="51" t="s">
+        <v>423</v>
+      </c>
       <c r="AW62" s="80"/>
       <c r="AX62" s="54">
         <f>K62</f>
@@ -30713,10 +30783,12 @@
       <c r="AZ62" s="51"/>
       <c r="BA62" s="51"/>
       <c r="BB62" s="51"/>
-      <c r="BC62" s="51"/>
-      <c r="BD62" s="54">
+      <c r="BC62" s="51" t="s">
+        <v>425</v>
+      </c>
+      <c r="BD62" s="54" t="str">
         <f>AP62</f>
-        <v>0</v>
+        <v>MG1CS022</v>
       </c>
       <c r="BE62" s="51" t="s">
         <v>648</v>
@@ -30724,7 +30796,9 @@
       <c r="BF62" s="51" t="s">
         <v>542</v>
       </c>
-      <c r="BG62" s="51"/>
+      <c r="BG62" s="51" t="s">
+        <v>467</v>
+      </c>
       <c r="BH62" s="51" t="s">
         <v>428</v>
       </c>
@@ -30877,7 +30951,9 @@
         <v>653</v>
       </c>
       <c r="CW62" s="81"/>
-      <c r="CX62" s="51"/>
+      <c r="CX62" s="51" t="s">
+        <v>658</v>
+      </c>
       <c r="CY62" s="51" t="s">
         <v>647</v>
       </c>
@@ -31134,35 +31210,35 @@
       <c r="S64" s="47"/>
       <c r="T64" s="47" t="b">
         <f>T62=T63</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U64" s="47" t="b">
         <f t="shared" ref="U64:AZ64" si="367">U62=U63</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB64" s="47" t="b">
         <f t="shared" si="367"/>
@@ -31170,7 +31246,7 @@
       </c>
       <c r="AC64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD64" s="47" t="b">
         <f t="shared" si="367"/>
@@ -31186,7 +31262,7 @@
       </c>
       <c r="AG64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH64" s="47" t="b">
         <f t="shared" si="367"/>
@@ -31222,7 +31298,7 @@
       </c>
       <c r="AP64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ64" s="47" t="b">
         <f t="shared" si="367"/>
@@ -31246,7 +31322,7 @@
       </c>
       <c r="AV64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW64" s="47" t="b">
         <f t="shared" si="367"/>
@@ -31272,11 +31348,11 @@
       </c>
       <c r="BC64" s="47" t="b">
         <f t="shared" ref="BC64:BH64" si="368">BC62=BC63</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD64" s="47" t="b">
         <f t="shared" si="368"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE64" s="47" t="b">
         <f t="shared" si="368"/>
@@ -31288,7 +31364,7 @@
       </c>
       <c r="BG64" s="47" t="b">
         <f t="shared" si="368"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH64" s="47" t="b">
         <f t="shared" si="368"/>
@@ -31613,11 +31689,13 @@
     <hyperlink ref="I50" r:id="rId14" xr:uid="{897A2AE7-E44B-4CD8-AFF4-98F2808E0093}"/>
     <hyperlink ref="I53" r:id="rId15" xr:uid="{F82E2495-3A0B-44B2-96ED-A174516D7C12}"/>
     <hyperlink ref="I56" r:id="rId16" xr:uid="{44C25546-B77C-4897-8B99-F969CFAF9914}"/>
+    <hyperlink ref="I59" r:id="rId17" xr:uid="{555B6F2A-7B37-4C98-9068-D0D153D97E20}"/>
+    <hyperlink ref="I62" r:id="rId18" xr:uid="{FFA1DC6E-3907-486F-BE7F-B08E581F4198}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId17"/>
-  <drawing r:id="rId18"/>
-  <legacyDrawing r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+  <drawing r:id="rId20"/>
+  <legacyDrawing r:id="rId21"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="1749" yWindow="937" count="4">

--- a/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
+++ b/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC487830-2BCE-47FB-B336-8AE94D55A3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C90661-3624-44A3-96DC-7B366CC5821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
@@ -3471,10 +3471,10 @@
     <t>37820-6WZ-M71</t>
   </si>
   <si>
-    <t>https://rb-pde-int.bosch.com:8881/app/ShowJob/16406</t>
-  </si>
-  <si>
-    <t>WF16408</t>
+    <t>WF16413</t>
+  </si>
+  <si>
+    <t>WF16414</t>
   </si>
 </sst>
 </file>
@@ -4312,24 +4312,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4348,7 +4330,25 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12611,35 +12611,35 @@
     </row>
     <row r="2" spans="1:104">
       <c r="A2" s="39"/>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
     </row>
     <row r="3" spans="1:104" ht="4.5" customHeight="1">
       <c r="A3" s="39"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
     </row>
     <row r="4" spans="1:104" ht="4.5" customHeight="1">
       <c r="A4" s="39"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
     </row>
     <row r="5" spans="1:104" s="41" customFormat="1" ht="18.75" customHeight="1">
       <c r="C5" s="67"/>
@@ -12689,75 +12689,75 @@
       <c r="CZ5" s="67"/>
     </row>
     <row r="6" spans="1:104" ht="18" customHeight="1">
-      <c r="B6" s="115" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="114" t="s">
+      <c r="B6" s="122" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="121" t="s">
         <v>307</v>
       </c>
-      <c r="N6" s="114"/>
-      <c r="O6" s="114" t="s">
+      <c r="N6" s="121"/>
+      <c r="O6" s="121" t="s">
         <v>308</v>
       </c>
-      <c r="P6" s="114"/>
+      <c r="P6" s="121"/>
       <c r="Q6" s="60" t="s">
         <v>349</v>
       </c>
       <c r="R6" s="60"/>
       <c r="S6" s="60"/>
-      <c r="T6" s="111" t="s">
+      <c r="T6" s="120" t="s">
         <v>101</v>
       </c>
-      <c r="U6" s="111"/>
-      <c r="V6" s="111"/>
-      <c r="W6" s="111"/>
-      <c r="X6" s="111"/>
-      <c r="Y6" s="111"/>
-      <c r="Z6" s="111"/>
-      <c r="AA6" s="111"/>
-      <c r="AB6" s="112" t="s">
+      <c r="U6" s="120"/>
+      <c r="V6" s="120"/>
+      <c r="W6" s="120"/>
+      <c r="X6" s="120"/>
+      <c r="Y6" s="120"/>
+      <c r="Z6" s="120"/>
+      <c r="AA6" s="120"/>
+      <c r="AB6" s="116" t="s">
         <v>125</v>
       </c>
-      <c r="AC6" s="112"/>
-      <c r="AD6" s="112"/>
-      <c r="AE6" s="112"/>
-      <c r="AF6" s="112"/>
-      <c r="AG6" s="112"/>
-      <c r="AH6" s="112"/>
-      <c r="AI6" s="112"/>
-      <c r="AJ6" s="112"/>
-      <c r="AK6" s="112"/>
-      <c r="AL6" s="113" t="s">
+      <c r="AC6" s="116"/>
+      <c r="AD6" s="116"/>
+      <c r="AE6" s="116"/>
+      <c r="AF6" s="116"/>
+      <c r="AG6" s="116"/>
+      <c r="AH6" s="116"/>
+      <c r="AI6" s="116"/>
+      <c r="AJ6" s="116"/>
+      <c r="AK6" s="116"/>
+      <c r="AL6" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="AM6" s="113"/>
-      <c r="AN6" s="113"/>
-      <c r="AO6" s="113"/>
-      <c r="AP6" s="113"/>
-      <c r="AQ6" s="112" t="s">
+      <c r="AM6" s="117"/>
+      <c r="AN6" s="117"/>
+      <c r="AO6" s="117"/>
+      <c r="AP6" s="117"/>
+      <c r="AQ6" s="116" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="112"/>
-      <c r="AS6" s="112"/>
-      <c r="AT6" s="112"/>
-      <c r="AU6" s="112"/>
-      <c r="AV6" s="113" t="s">
+      <c r="AR6" s="116"/>
+      <c r="AS6" s="116"/>
+      <c r="AT6" s="116"/>
+      <c r="AU6" s="116"/>
+      <c r="AV6" s="117" t="s">
         <v>165</v>
       </c>
-      <c r="AW6" s="113"/>
-      <c r="AX6" s="113"/>
-      <c r="AY6" s="113"/>
-      <c r="AZ6" s="113"/>
+      <c r="AW6" s="117"/>
+      <c r="AX6" s="117"/>
+      <c r="AY6" s="117"/>
+      <c r="AZ6" s="117"/>
       <c r="BA6" s="48"/>
       <c r="BB6" s="48"/>
       <c r="BC6" s="60" t="s">
@@ -12855,25 +12855,25 @@
       <c r="CK6" s="64">
         <v>14</v>
       </c>
-      <c r="CL6" s="119" t="s">
+      <c r="CL6" s="113" t="s">
         <v>193</v>
       </c>
-      <c r="CM6" s="120"/>
-      <c r="CN6" s="120"/>
-      <c r="CO6" s="120"/>
-      <c r="CP6" s="120"/>
-      <c r="CQ6" s="120"/>
-      <c r="CR6" s="121"/>
-      <c r="CS6" s="116" t="s">
+      <c r="CM6" s="114"/>
+      <c r="CN6" s="114"/>
+      <c r="CO6" s="114"/>
+      <c r="CP6" s="114"/>
+      <c r="CQ6" s="114"/>
+      <c r="CR6" s="115"/>
+      <c r="CS6" s="110" t="s">
         <v>373</v>
       </c>
-      <c r="CT6" s="117"/>
-      <c r="CU6" s="117"/>
-      <c r="CV6" s="117"/>
-      <c r="CW6" s="117"/>
-      <c r="CX6" s="117"/>
-      <c r="CY6" s="117"/>
-      <c r="CZ6" s="118"/>
+      <c r="CT6" s="111"/>
+      <c r="CU6" s="111"/>
+      <c r="CV6" s="111"/>
+      <c r="CW6" s="111"/>
+      <c r="CX6" s="111"/>
+      <c r="CY6" s="111"/>
+      <c r="CZ6" s="112"/>
     </row>
     <row r="7" spans="1:104" ht="114" collapsed="1">
       <c r="A7" s="66" t="s">
@@ -13059,38 +13059,38 @@
       <c r="BI7" s="65" t="s">
         <v>340</v>
       </c>
-      <c r="BJ7" s="122" t="s">
+      <c r="BJ7" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="BK7" s="122"/>
-      <c r="BL7" s="122"/>
-      <c r="BM7" s="122"/>
-      <c r="BN7" s="122"/>
-      <c r="BO7" s="122"/>
-      <c r="BP7" s="122"/>
-      <c r="BQ7" s="122"/>
-      <c r="BR7" s="122"/>
-      <c r="BS7" s="122"/>
-      <c r="BT7" s="122"/>
-      <c r="BU7" s="122"/>
-      <c r="BV7" s="122"/>
-      <c r="BW7" s="122"/>
-      <c r="BX7" s="122" t="s">
+      <c r="BK7" s="118"/>
+      <c r="BL7" s="118"/>
+      <c r="BM7" s="118"/>
+      <c r="BN7" s="118"/>
+      <c r="BO7" s="118"/>
+      <c r="BP7" s="118"/>
+      <c r="BQ7" s="118"/>
+      <c r="BR7" s="118"/>
+      <c r="BS7" s="118"/>
+      <c r="BT7" s="118"/>
+      <c r="BU7" s="118"/>
+      <c r="BV7" s="118"/>
+      <c r="BW7" s="118"/>
+      <c r="BX7" s="118" t="s">
         <v>300</v>
       </c>
-      <c r="BY7" s="122"/>
-      <c r="BZ7" s="122"/>
-      <c r="CA7" s="122"/>
-      <c r="CB7" s="122"/>
-      <c r="CC7" s="122"/>
-      <c r="CD7" s="122"/>
-      <c r="CE7" s="122"/>
-      <c r="CF7" s="122"/>
-      <c r="CG7" s="122"/>
-      <c r="CH7" s="122"/>
-      <c r="CI7" s="122"/>
-      <c r="CJ7" s="122"/>
-      <c r="CK7" s="122"/>
+      <c r="BY7" s="118"/>
+      <c r="BZ7" s="118"/>
+      <c r="CA7" s="118"/>
+      <c r="CB7" s="118"/>
+      <c r="CC7" s="118"/>
+      <c r="CD7" s="118"/>
+      <c r="CE7" s="118"/>
+      <c r="CF7" s="118"/>
+      <c r="CG7" s="118"/>
+      <c r="CH7" s="118"/>
+      <c r="CI7" s="118"/>
+      <c r="CJ7" s="118"/>
+      <c r="CK7" s="118"/>
       <c r="CL7" s="48" t="s">
         <v>370</v>
       </c>
@@ -31510,12 +31510,6 @@
   </sheetData>
   <autoFilter ref="A10:CZ58" xr:uid="{03E47C1A-8C76-40C7-A467-A5F175EC7551}"/>
   <mergeCells count="13">
-    <mergeCell ref="CS6:CZ6"/>
-    <mergeCell ref="CL6:CR6"/>
-    <mergeCell ref="AQ6:AU6"/>
-    <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="BJ7:BW7"/>
-    <mergeCell ref="BX7:CK7"/>
     <mergeCell ref="B2:H4"/>
     <mergeCell ref="T6:AA6"/>
     <mergeCell ref="AB6:AK6"/>
@@ -31523,6 +31517,12 @@
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="O6:P6"/>
+    <mergeCell ref="CS6:CZ6"/>
+    <mergeCell ref="CL6:CR6"/>
+    <mergeCell ref="AQ6:AU6"/>
+    <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="BJ7:BW7"/>
+    <mergeCell ref="BX7:CK7"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <conditionalFormatting sqref="T13:AZ13 BC13:CR13 BC16:CR16">

--- a/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
+++ b/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C90661-3624-44A3-96DC-7B366CC5821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D831F4-41F2-45E9-8906-14021EC527BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3124" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="667">
   <si>
     <t>HONDA 62XS CONTAINER</t>
   </si>
@@ -3426,55 +3426,73 @@
 Kurata-san</t>
   </si>
   <si>
+    <t>01</t>
+  </si>
+  <si>
     <t>37820-6WZ-M610-M6</t>
   </si>
   <si>
+    <t>6WZX</t>
+  </si>
+  <si>
+    <t>0261S10BN8</t>
+  </si>
+  <si>
+    <t>0261B00E0B</t>
+  </si>
+  <si>
     <t>37805-6WZ-M610</t>
   </si>
   <si>
     <t>01-28-41-00-01</t>
   </si>
   <si>
+    <t>37820-6WZ-M61</t>
+  </si>
+  <si>
     <t>C7C</t>
   </si>
   <si>
-    <t>6WZX</t>
-  </si>
-  <si>
-    <t>MY28</t>
-  </si>
-  <si>
-    <t>Brazil|Paraguay</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
     <t>37820-6WZ-M710-M6</t>
   </si>
   <si>
+    <t>0261S10BN9</t>
+  </si>
+  <si>
+    <t>0261B00E0C</t>
+  </si>
+  <si>
     <t>37805-6WZ-M710</t>
   </si>
   <si>
     <t>01-28-41-01-01</t>
   </si>
   <si>
+    <t>37820-6WZ-M71</t>
+  </si>
+  <si>
     <t>DTW</t>
   </si>
   <si>
-    <t>6WZX - MP0 event</t>
-  </si>
-  <si>
-    <t>37820-6WZ-M61</t>
-  </si>
-  <si>
-    <t>37820-6WZ-M71</t>
-  </si>
-  <si>
-    <t>WF16413</t>
-  </si>
-  <si>
-    <t>WF16414</t>
+    <t>WRV</t>
+  </si>
+  <si>
+    <t>6WZX for MP0 event</t>
+  </si>
+  <si>
+    <t>MG1CS022_62XSC_V037</t>
+  </si>
+  <si>
+    <t>MG1CS022_6WZXSC_V037_L8-2_FFV_Lo_0x_BL013_MP0_VIN_IMMO_ON.hex</t>
+  </si>
+  <si>
+    <t>MG1CS022_6WZXSC_V037_L8-2_FFV_Hi_0x_BL013_MP0_VIN_IMMO_ON.hex</t>
+  </si>
+  <si>
+    <t>WF16418</t>
+  </si>
+  <si>
+    <t>WF16419</t>
   </si>
 </sst>
 </file>
@@ -4312,6 +4330,24 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4330,25 +4366,7 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12611,35 +12629,35 @@
     </row>
     <row r="2" spans="1:104">
       <c r="A2" s="39"/>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
     </row>
     <row r="3" spans="1:104" ht="4.5" customHeight="1">
       <c r="A3" s="39"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
     </row>
     <row r="4" spans="1:104" ht="4.5" customHeight="1">
       <c r="A4" s="39"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
     </row>
     <row r="5" spans="1:104" s="41" customFormat="1" ht="18.75" customHeight="1">
       <c r="C5" s="67"/>
@@ -12689,75 +12707,75 @@
       <c r="CZ5" s="67"/>
     </row>
     <row r="6" spans="1:104" ht="18" customHeight="1">
-      <c r="B6" s="122" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="121" t="s">
+      <c r="B6" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="115"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="114" t="s">
         <v>307</v>
       </c>
-      <c r="N6" s="121"/>
-      <c r="O6" s="121" t="s">
+      <c r="N6" s="114"/>
+      <c r="O6" s="114" t="s">
         <v>308</v>
       </c>
-      <c r="P6" s="121"/>
+      <c r="P6" s="114"/>
       <c r="Q6" s="60" t="s">
         <v>349</v>
       </c>
       <c r="R6" s="60"/>
       <c r="S6" s="60"/>
-      <c r="T6" s="120" t="s">
+      <c r="T6" s="111" t="s">
         <v>101</v>
       </c>
-      <c r="U6" s="120"/>
-      <c r="V6" s="120"/>
-      <c r="W6" s="120"/>
-      <c r="X6" s="120"/>
-      <c r="Y6" s="120"/>
-      <c r="Z6" s="120"/>
-      <c r="AA6" s="120"/>
-      <c r="AB6" s="116" t="s">
+      <c r="U6" s="111"/>
+      <c r="V6" s="111"/>
+      <c r="W6" s="111"/>
+      <c r="X6" s="111"/>
+      <c r="Y6" s="111"/>
+      <c r="Z6" s="111"/>
+      <c r="AA6" s="111"/>
+      <c r="AB6" s="112" t="s">
         <v>125</v>
       </c>
-      <c r="AC6" s="116"/>
-      <c r="AD6" s="116"/>
-      <c r="AE6" s="116"/>
-      <c r="AF6" s="116"/>
-      <c r="AG6" s="116"/>
-      <c r="AH6" s="116"/>
-      <c r="AI6" s="116"/>
-      <c r="AJ6" s="116"/>
-      <c r="AK6" s="116"/>
-      <c r="AL6" s="117" t="s">
+      <c r="AC6" s="112"/>
+      <c r="AD6" s="112"/>
+      <c r="AE6" s="112"/>
+      <c r="AF6" s="112"/>
+      <c r="AG6" s="112"/>
+      <c r="AH6" s="112"/>
+      <c r="AI6" s="112"/>
+      <c r="AJ6" s="112"/>
+      <c r="AK6" s="112"/>
+      <c r="AL6" s="113" t="s">
         <v>126</v>
       </c>
-      <c r="AM6" s="117"/>
-      <c r="AN6" s="117"/>
-      <c r="AO6" s="117"/>
-      <c r="AP6" s="117"/>
-      <c r="AQ6" s="116" t="s">
+      <c r="AM6" s="113"/>
+      <c r="AN6" s="113"/>
+      <c r="AO6" s="113"/>
+      <c r="AP6" s="113"/>
+      <c r="AQ6" s="112" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="116"/>
-      <c r="AS6" s="116"/>
-      <c r="AT6" s="116"/>
-      <c r="AU6" s="116"/>
-      <c r="AV6" s="117" t="s">
+      <c r="AR6" s="112"/>
+      <c r="AS6" s="112"/>
+      <c r="AT6" s="112"/>
+      <c r="AU6" s="112"/>
+      <c r="AV6" s="113" t="s">
         <v>165</v>
       </c>
-      <c r="AW6" s="117"/>
-      <c r="AX6" s="117"/>
-      <c r="AY6" s="117"/>
-      <c r="AZ6" s="117"/>
+      <c r="AW6" s="113"/>
+      <c r="AX6" s="113"/>
+      <c r="AY6" s="113"/>
+      <c r="AZ6" s="113"/>
       <c r="BA6" s="48"/>
       <c r="BB6" s="48"/>
       <c r="BC6" s="60" t="s">
@@ -12855,25 +12873,25 @@
       <c r="CK6" s="64">
         <v>14</v>
       </c>
-      <c r="CL6" s="113" t="s">
+      <c r="CL6" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="CM6" s="114"/>
-      <c r="CN6" s="114"/>
-      <c r="CO6" s="114"/>
-      <c r="CP6" s="114"/>
-      <c r="CQ6" s="114"/>
-      <c r="CR6" s="115"/>
-      <c r="CS6" s="110" t="s">
+      <c r="CM6" s="120"/>
+      <c r="CN6" s="120"/>
+      <c r="CO6" s="120"/>
+      <c r="CP6" s="120"/>
+      <c r="CQ6" s="120"/>
+      <c r="CR6" s="121"/>
+      <c r="CS6" s="116" t="s">
         <v>373</v>
       </c>
-      <c r="CT6" s="111"/>
-      <c r="CU6" s="111"/>
-      <c r="CV6" s="111"/>
-      <c r="CW6" s="111"/>
-      <c r="CX6" s="111"/>
-      <c r="CY6" s="111"/>
-      <c r="CZ6" s="112"/>
+      <c r="CT6" s="117"/>
+      <c r="CU6" s="117"/>
+      <c r="CV6" s="117"/>
+      <c r="CW6" s="117"/>
+      <c r="CX6" s="117"/>
+      <c r="CY6" s="117"/>
+      <c r="CZ6" s="118"/>
     </row>
     <row r="7" spans="1:104" ht="114" collapsed="1">
       <c r="A7" s="66" t="s">
@@ -13059,38 +13077,38 @@
       <c r="BI7" s="65" t="s">
         <v>340</v>
       </c>
-      <c r="BJ7" s="118" t="s">
+      <c r="BJ7" s="122" t="s">
         <v>299</v>
       </c>
-      <c r="BK7" s="118"/>
-      <c r="BL7" s="118"/>
-      <c r="BM7" s="118"/>
-      <c r="BN7" s="118"/>
-      <c r="BO7" s="118"/>
-      <c r="BP7" s="118"/>
-      <c r="BQ7" s="118"/>
-      <c r="BR7" s="118"/>
-      <c r="BS7" s="118"/>
-      <c r="BT7" s="118"/>
-      <c r="BU7" s="118"/>
-      <c r="BV7" s="118"/>
-      <c r="BW7" s="118"/>
-      <c r="BX7" s="118" t="s">
+      <c r="BK7" s="122"/>
+      <c r="BL7" s="122"/>
+      <c r="BM7" s="122"/>
+      <c r="BN7" s="122"/>
+      <c r="BO7" s="122"/>
+      <c r="BP7" s="122"/>
+      <c r="BQ7" s="122"/>
+      <c r="BR7" s="122"/>
+      <c r="BS7" s="122"/>
+      <c r="BT7" s="122"/>
+      <c r="BU7" s="122"/>
+      <c r="BV7" s="122"/>
+      <c r="BW7" s="122"/>
+      <c r="BX7" s="122" t="s">
         <v>300</v>
       </c>
-      <c r="BY7" s="118"/>
-      <c r="BZ7" s="118"/>
-      <c r="CA7" s="118"/>
-      <c r="CB7" s="118"/>
-      <c r="CC7" s="118"/>
-      <c r="CD7" s="118"/>
-      <c r="CE7" s="118"/>
-      <c r="CF7" s="118"/>
-      <c r="CG7" s="118"/>
-      <c r="CH7" s="118"/>
-      <c r="CI7" s="118"/>
-      <c r="CJ7" s="118"/>
-      <c r="CK7" s="118"/>
+      <c r="BY7" s="122"/>
+      <c r="BZ7" s="122"/>
+      <c r="CA7" s="122"/>
+      <c r="CB7" s="122"/>
+      <c r="CC7" s="122"/>
+      <c r="CD7" s="122"/>
+      <c r="CE7" s="122"/>
+      <c r="CF7" s="122"/>
+      <c r="CG7" s="122"/>
+      <c r="CH7" s="122"/>
+      <c r="CI7" s="122"/>
+      <c r="CJ7" s="122"/>
+      <c r="CK7" s="122"/>
       <c r="CL7" s="48" t="s">
         <v>370</v>
       </c>
@@ -26901,7 +26919,7 @@
       </c>
       <c r="O50" s="51" t="str">
         <f>IF(COUNTIF(C52:CZ52,"FALSE")&gt;0,"NG","OK")</f>
-        <v>OK</v>
+        <v>NG</v>
       </c>
       <c r="P50" s="51" t="s">
         <v>643</v>
@@ -27171,8 +27189,8 @@
       <c r="CP50" s="51" t="s">
         <v>438</v>
       </c>
-      <c r="CQ50" s="51">
-        <v>1</v>
+      <c r="CQ50" s="77" t="s">
+        <v>644</v>
       </c>
       <c r="CR50" s="81" t="s">
         <v>240</v>
@@ -27805,7 +27823,7 @@
       </c>
       <c r="CQ52" s="47" t="b">
         <f t="shared" ref="CQ52" si="300">CQ50=CQ51</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR52" s="47" t="s">
         <v>262</v>
@@ -27879,7 +27897,7 @@
       </c>
       <c r="O53" s="51" t="str">
         <f>IF(COUNTIF(C55:CZ55,"FALSE")&gt;0,"NG","OK")</f>
-        <v>OK</v>
+        <v>NG</v>
       </c>
       <c r="P53" s="51" t="s">
         <v>643</v>
@@ -28149,8 +28167,8 @@
       <c r="CP53" s="51" t="s">
         <v>438</v>
       </c>
-      <c r="CQ53" s="51">
-        <v>1</v>
+      <c r="CQ53" s="77" t="s">
+        <v>644</v>
       </c>
       <c r="CR53" s="81" t="s">
         <v>240</v>
@@ -28783,7 +28801,7 @@
       </c>
       <c r="CQ55" s="47" t="b">
         <f t="shared" ref="CQ55" si="318">CQ53=CQ54</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR55" s="47" t="s">
         <v>262</v>
@@ -28857,7 +28875,7 @@
       </c>
       <c r="O56" s="51" t="str">
         <f>IF(COUNTIF(C58:CZ58,"FALSE")&gt;0,"NG","OK")</f>
-        <v>OK</v>
+        <v>NG</v>
       </c>
       <c r="P56" s="51" t="s">
         <v>643</v>
@@ -29127,8 +29145,8 @@
       <c r="CP56" s="51" t="s">
         <v>438</v>
       </c>
-      <c r="CQ56" s="51">
-        <v>1</v>
+      <c r="CQ56" s="77" t="s">
+        <v>644</v>
       </c>
       <c r="CR56" s="81" t="s">
         <v>240</v>
@@ -29761,7 +29779,7 @@
       </c>
       <c r="CQ58" s="47" t="b">
         <f t="shared" ref="CQ58" si="336">CQ56=CQ57</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR58" s="47" t="s">
         <v>262</v>
@@ -29798,7 +29816,7 @@
         <v>17</v>
       </c>
       <c r="C59" s="52">
-        <v>46321.406064814815</v>
+        <v>46325.341377314813</v>
       </c>
       <c r="D59" s="51" t="s">
         <v>254</v>
@@ -29807,13 +29825,13 @@
       <c r="F59" s="51"/>
       <c r="G59" s="52"/>
       <c r="H59" s="51" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="I59" s="78" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="J59" s="53" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="K59" s="53"/>
       <c r="L59" s="51"/>
@@ -29837,7 +29855,7 @@
         <v>40</v>
       </c>
       <c r="U59" s="51" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="V59" s="51" t="s">
         <v>39</v>
@@ -29858,7 +29876,7 @@
         <v>405</v>
       </c>
       <c r="AB59" s="51" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AC59" s="51">
         <v>93</v>
@@ -29869,8 +29887,8 @@
       <c r="AE59" s="51">
         <v>1.5</v>
       </c>
-      <c r="AF59" s="51" t="s">
-        <v>649</v>
+      <c r="AF59" s="51">
+        <v>2028</v>
       </c>
       <c r="AG59" s="51" t="s">
         <v>389</v>
@@ -29882,9 +29900,11 @@
         <v>409</v>
       </c>
       <c r="AJ59" s="51" t="s">
-        <v>650</v>
-      </c>
-      <c r="AK59" s="51"/>
+        <v>410</v>
+      </c>
+      <c r="AK59" s="51">
+        <v>4</v>
+      </c>
       <c r="AL59" s="51">
         <v>159</v>
       </c>
@@ -29892,8 +29912,12 @@
         <f>SUBSTITUTE(SUBSTITUTE(J59," ",""),"-","")</f>
         <v>378206WZM610M6</v>
       </c>
-      <c r="AN59" s="51"/>
-      <c r="AO59" s="51"/>
+      <c r="AN59" s="77" t="s">
+        <v>647</v>
+      </c>
+      <c r="AO59" s="77" t="s">
+        <v>648</v>
+      </c>
       <c r="AP59" s="51" t="s">
         <v>404</v>
       </c>
@@ -29909,20 +29933,26 @@
         <f>K59</f>
         <v>0</v>
       </c>
-      <c r="AT59" s="51"/>
+      <c r="AT59" s="51" t="s">
+        <v>660</v>
+      </c>
       <c r="AU59" s="51" t="s">
         <v>422</v>
       </c>
       <c r="AV59" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW59" s="80"/>
+      <c r="AW59" s="77"/>
       <c r="AX59" s="54">
         <f>K59</f>
         <v>0</v>
       </c>
-      <c r="AY59" s="51"/>
-      <c r="AZ59" s="51"/>
+      <c r="AY59" s="51" t="s">
+        <v>662</v>
+      </c>
+      <c r="AZ59" s="51" t="s">
+        <v>663</v>
+      </c>
       <c r="BA59" s="51"/>
       <c r="BB59" s="51"/>
       <c r="BC59" s="51" t="s">
@@ -29933,7 +29963,7 @@
         <v>MG1CS022</v>
       </c>
       <c r="BE59" s="51" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="BF59" s="51" t="s">
         <v>542</v>
@@ -29945,7 +29975,7 @@
         <v>428</v>
       </c>
       <c r="BI59" s="51" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="BJ59" s="54" t="str">
         <f t="shared" si="319"/>
@@ -30076,7 +30106,7 @@
         <v>304</v>
       </c>
       <c r="CQ59" s="77" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="CR59" s="81"/>
       <c r="CS59" s="54" t="str">
@@ -30084,23 +30114,23 @@
         <v>37820-6WZ-M610-M6</v>
       </c>
       <c r="CT59" s="77" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="CU59" s="51" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="CV59" s="51" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="CW59" s="81"/>
       <c r="CX59" s="51" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="CY59" s="51" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="CZ59" s="51" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
     </row>
     <row r="60" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
@@ -30420,7 +30450,7 @@
       </c>
       <c r="AK61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL61" s="47" t="b">
         <f t="shared" si="350"/>
@@ -30432,11 +30462,11 @@
       </c>
       <c r="AN61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP61" s="47" t="b">
         <f t="shared" si="350"/>
@@ -30456,7 +30486,7 @@
       </c>
       <c r="AT61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU61" s="47" t="b">
         <f t="shared" si="350"/>
@@ -30476,11 +30506,11 @@
       </c>
       <c r="AY61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA61" s="47" t="s">
         <v>262</v>
@@ -30656,7 +30686,7 @@
         <v>18</v>
       </c>
       <c r="C62" s="52">
-        <v>46321.406076388892</v>
+        <v>46325.34138888889</v>
       </c>
       <c r="D62" s="51" t="s">
         <v>254</v>
@@ -30665,13 +30695,13 @@
       <c r="F62" s="51"/>
       <c r="G62" s="52"/>
       <c r="H62" s="51" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="I62" s="78" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="J62" s="53" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="K62" s="53"/>
       <c r="L62" s="51"/>
@@ -30695,7 +30725,7 @@
         <v>40</v>
       </c>
       <c r="U62" s="51" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="V62" s="51" t="s">
         <v>39</v>
@@ -30716,7 +30746,7 @@
         <v>405</v>
       </c>
       <c r="AB62" s="51" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AC62" s="51">
         <v>93</v>
@@ -30727,8 +30757,8 @@
       <c r="AE62" s="51">
         <v>1.5</v>
       </c>
-      <c r="AF62" s="51" t="s">
-        <v>649</v>
+      <c r="AF62" s="51">
+        <v>2028</v>
       </c>
       <c r="AG62" s="51" t="s">
         <v>389</v>
@@ -30740,9 +30770,11 @@
         <v>409</v>
       </c>
       <c r="AJ62" s="51" t="s">
-        <v>650</v>
-      </c>
-      <c r="AK62" s="51"/>
+        <v>410</v>
+      </c>
+      <c r="AK62" s="51">
+        <v>4</v>
+      </c>
       <c r="AL62" s="51">
         <v>159</v>
       </c>
@@ -30750,8 +30782,12 @@
         <f>SUBSTITUTE(SUBSTITUTE(J62," ",""),"-","")</f>
         <v>378206WZM710M6</v>
       </c>
-      <c r="AN62" s="51"/>
-      <c r="AO62" s="51"/>
+      <c r="AN62" s="77" t="s">
+        <v>654</v>
+      </c>
+      <c r="AO62" s="77" t="s">
+        <v>655</v>
+      </c>
       <c r="AP62" s="51" t="s">
         <v>404</v>
       </c>
@@ -30767,20 +30803,26 @@
         <f>K62</f>
         <v>0</v>
       </c>
-      <c r="AT62" s="51"/>
+      <c r="AT62" s="51" t="s">
+        <v>660</v>
+      </c>
       <c r="AU62" s="51" t="s">
         <v>422</v>
       </c>
       <c r="AV62" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW62" s="80"/>
+      <c r="AW62" s="77"/>
       <c r="AX62" s="54">
         <f>K62</f>
         <v>0</v>
       </c>
-      <c r="AY62" s="51"/>
-      <c r="AZ62" s="51"/>
+      <c r="AY62" s="51" t="s">
+        <v>662</v>
+      </c>
+      <c r="AZ62" s="51" t="s">
+        <v>664</v>
+      </c>
       <c r="BA62" s="51"/>
       <c r="BB62" s="51"/>
       <c r="BC62" s="51" t="s">
@@ -30791,7 +30833,7 @@
         <v>MG1CS022</v>
       </c>
       <c r="BE62" s="51" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="BF62" s="51" t="s">
         <v>542</v>
@@ -30803,7 +30845,7 @@
         <v>428</v>
       </c>
       <c r="BI62" s="51" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="BJ62" s="54" t="str">
         <f t="shared" si="319"/>
@@ -30934,7 +30976,7 @@
         <v>304</v>
       </c>
       <c r="CQ62" s="77" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="CR62" s="81"/>
       <c r="CS62" s="54" t="str">
@@ -30942,23 +30984,23 @@
         <v>37820-6WZ-M710-M6</v>
       </c>
       <c r="CT62" s="77" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="CU62" s="51" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="CV62" s="51" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="CW62" s="81"/>
       <c r="CX62" s="51" t="s">
         <v>658</v>
       </c>
       <c r="CY62" s="51" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="CZ62" s="51" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="63" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
@@ -31278,7 +31320,7 @@
       </c>
       <c r="AK64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL64" s="47" t="b">
         <f t="shared" si="367"/>
@@ -31290,11 +31332,11 @@
       </c>
       <c r="AN64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP64" s="47" t="b">
         <f t="shared" si="367"/>
@@ -31314,7 +31356,7 @@
       </c>
       <c r="AT64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU64" s="47" t="b">
         <f t="shared" si="367"/>
@@ -31334,11 +31376,11 @@
       </c>
       <c r="AY64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA64" s="47" t="s">
         <v>262</v>
@@ -31510,6 +31552,12 @@
   </sheetData>
   <autoFilter ref="A10:CZ58" xr:uid="{03E47C1A-8C76-40C7-A467-A5F175EC7551}"/>
   <mergeCells count="13">
+    <mergeCell ref="CS6:CZ6"/>
+    <mergeCell ref="CL6:CR6"/>
+    <mergeCell ref="AQ6:AU6"/>
+    <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="BJ7:BW7"/>
+    <mergeCell ref="BX7:CK7"/>
     <mergeCell ref="B2:H4"/>
     <mergeCell ref="T6:AA6"/>
     <mergeCell ref="AB6:AK6"/>
@@ -31517,12 +31565,6 @@
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="O6:P6"/>
-    <mergeCell ref="CS6:CZ6"/>
-    <mergeCell ref="CL6:CR6"/>
-    <mergeCell ref="AQ6:AU6"/>
-    <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="BJ7:BW7"/>
-    <mergeCell ref="BX7:CK7"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <conditionalFormatting sqref="T13:AZ13 BC13:CR13 BC16:CR16">
@@ -31689,8 +31731,8 @@
     <hyperlink ref="I50" r:id="rId14" xr:uid="{897A2AE7-E44B-4CD8-AFF4-98F2808E0093}"/>
     <hyperlink ref="I53" r:id="rId15" xr:uid="{F82E2495-3A0B-44B2-96ED-A174516D7C12}"/>
     <hyperlink ref="I56" r:id="rId16" xr:uid="{44C25546-B77C-4897-8B99-F969CFAF9914}"/>
-    <hyperlink ref="I59" r:id="rId17" xr:uid="{555B6F2A-7B37-4C98-9068-D0D153D97E20}"/>
-    <hyperlink ref="I62" r:id="rId18" xr:uid="{FFA1DC6E-3907-486F-BE7F-B08E581F4198}"/>
+    <hyperlink ref="I59" r:id="rId17" xr:uid="{61270879-3C09-4908-BBC6-C8AC38E78AB0}"/>
+    <hyperlink ref="I62" r:id="rId18" xr:uid="{B7CFD406-1DE7-49F9-ADB7-9B8EEE8264A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>

--- a/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
+++ b/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D831F4-41F2-45E9-8906-14021EC527BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3453CA38-034A-458B-A531-E0C62F15A786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="668">
   <si>
     <t>HONDA 62XS CONTAINER</t>
   </si>
@@ -3489,10 +3489,13 @@
     <t>MG1CS022_6WZXSC_V037_L8-2_FFV_Hi_0x_BL013_MP0_VIN_IMMO_ON.hex</t>
   </si>
   <si>
-    <t>WF16418</t>
-  </si>
-  <si>
-    <t>WF16419</t>
+    <t>WF16424</t>
+  </si>
+  <si>
+    <t>WF16425</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -4330,24 +4333,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4366,7 +4351,25 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12629,35 +12632,35 @@
     </row>
     <row r="2" spans="1:104">
       <c r="A2" s="39"/>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
     </row>
     <row r="3" spans="1:104" ht="4.5" customHeight="1">
       <c r="A3" s="39"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
     </row>
     <row r="4" spans="1:104" ht="4.5" customHeight="1">
       <c r="A4" s="39"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
     </row>
     <row r="5" spans="1:104" s="41" customFormat="1" ht="18.75" customHeight="1">
       <c r="C5" s="67"/>
@@ -12707,75 +12710,75 @@
       <c r="CZ5" s="67"/>
     </row>
     <row r="6" spans="1:104" ht="18" customHeight="1">
-      <c r="B6" s="115" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="114" t="s">
+      <c r="B6" s="122" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="121" t="s">
         <v>307</v>
       </c>
-      <c r="N6" s="114"/>
-      <c r="O6" s="114" t="s">
+      <c r="N6" s="121"/>
+      <c r="O6" s="121" t="s">
         <v>308</v>
       </c>
-      <c r="P6" s="114"/>
+      <c r="P6" s="121"/>
       <c r="Q6" s="60" t="s">
         <v>349</v>
       </c>
       <c r="R6" s="60"/>
       <c r="S6" s="60"/>
-      <c r="T6" s="111" t="s">
+      <c r="T6" s="120" t="s">
         <v>101</v>
       </c>
-      <c r="U6" s="111"/>
-      <c r="V6" s="111"/>
-      <c r="W6" s="111"/>
-      <c r="X6" s="111"/>
-      <c r="Y6" s="111"/>
-      <c r="Z6" s="111"/>
-      <c r="AA6" s="111"/>
-      <c r="AB6" s="112" t="s">
+      <c r="U6" s="120"/>
+      <c r="V6" s="120"/>
+      <c r="W6" s="120"/>
+      <c r="X6" s="120"/>
+      <c r="Y6" s="120"/>
+      <c r="Z6" s="120"/>
+      <c r="AA6" s="120"/>
+      <c r="AB6" s="116" t="s">
         <v>125</v>
       </c>
-      <c r="AC6" s="112"/>
-      <c r="AD6" s="112"/>
-      <c r="AE6" s="112"/>
-      <c r="AF6" s="112"/>
-      <c r="AG6" s="112"/>
-      <c r="AH6" s="112"/>
-      <c r="AI6" s="112"/>
-      <c r="AJ6" s="112"/>
-      <c r="AK6" s="112"/>
-      <c r="AL6" s="113" t="s">
+      <c r="AC6" s="116"/>
+      <c r="AD6" s="116"/>
+      <c r="AE6" s="116"/>
+      <c r="AF6" s="116"/>
+      <c r="AG6" s="116"/>
+      <c r="AH6" s="116"/>
+      <c r="AI6" s="116"/>
+      <c r="AJ6" s="116"/>
+      <c r="AK6" s="116"/>
+      <c r="AL6" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="AM6" s="113"/>
-      <c r="AN6" s="113"/>
-      <c r="AO6" s="113"/>
-      <c r="AP6" s="113"/>
-      <c r="AQ6" s="112" t="s">
+      <c r="AM6" s="117"/>
+      <c r="AN6" s="117"/>
+      <c r="AO6" s="117"/>
+      <c r="AP6" s="117"/>
+      <c r="AQ6" s="116" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="112"/>
-      <c r="AS6" s="112"/>
-      <c r="AT6" s="112"/>
-      <c r="AU6" s="112"/>
-      <c r="AV6" s="113" t="s">
+      <c r="AR6" s="116"/>
+      <c r="AS6" s="116"/>
+      <c r="AT6" s="116"/>
+      <c r="AU6" s="116"/>
+      <c r="AV6" s="117" t="s">
         <v>165</v>
       </c>
-      <c r="AW6" s="113"/>
-      <c r="AX6" s="113"/>
-      <c r="AY6" s="113"/>
-      <c r="AZ6" s="113"/>
+      <c r="AW6" s="117"/>
+      <c r="AX6" s="117"/>
+      <c r="AY6" s="117"/>
+      <c r="AZ6" s="117"/>
       <c r="BA6" s="48"/>
       <c r="BB6" s="48"/>
       <c r="BC6" s="60" t="s">
@@ -12873,25 +12876,25 @@
       <c r="CK6" s="64">
         <v>14</v>
       </c>
-      <c r="CL6" s="119" t="s">
+      <c r="CL6" s="113" t="s">
         <v>193</v>
       </c>
-      <c r="CM6" s="120"/>
-      <c r="CN6" s="120"/>
-      <c r="CO6" s="120"/>
-      <c r="CP6" s="120"/>
-      <c r="CQ6" s="120"/>
-      <c r="CR6" s="121"/>
-      <c r="CS6" s="116" t="s">
+      <c r="CM6" s="114"/>
+      <c r="CN6" s="114"/>
+      <c r="CO6" s="114"/>
+      <c r="CP6" s="114"/>
+      <c r="CQ6" s="114"/>
+      <c r="CR6" s="115"/>
+      <c r="CS6" s="110" t="s">
         <v>373</v>
       </c>
-      <c r="CT6" s="117"/>
-      <c r="CU6" s="117"/>
-      <c r="CV6" s="117"/>
-      <c r="CW6" s="117"/>
-      <c r="CX6" s="117"/>
-      <c r="CY6" s="117"/>
-      <c r="CZ6" s="118"/>
+      <c r="CT6" s="111"/>
+      <c r="CU6" s="111"/>
+      <c r="CV6" s="111"/>
+      <c r="CW6" s="111"/>
+      <c r="CX6" s="111"/>
+      <c r="CY6" s="111"/>
+      <c r="CZ6" s="112"/>
     </row>
     <row r="7" spans="1:104" ht="114" collapsed="1">
       <c r="A7" s="66" t="s">
@@ -13077,38 +13080,38 @@
       <c r="BI7" s="65" t="s">
         <v>340</v>
       </c>
-      <c r="BJ7" s="122" t="s">
+      <c r="BJ7" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="BK7" s="122"/>
-      <c r="BL7" s="122"/>
-      <c r="BM7" s="122"/>
-      <c r="BN7" s="122"/>
-      <c r="BO7" s="122"/>
-      <c r="BP7" s="122"/>
-      <c r="BQ7" s="122"/>
-      <c r="BR7" s="122"/>
-      <c r="BS7" s="122"/>
-      <c r="BT7" s="122"/>
-      <c r="BU7" s="122"/>
-      <c r="BV7" s="122"/>
-      <c r="BW7" s="122"/>
-      <c r="BX7" s="122" t="s">
+      <c r="BK7" s="118"/>
+      <c r="BL7" s="118"/>
+      <c r="BM7" s="118"/>
+      <c r="BN7" s="118"/>
+      <c r="BO7" s="118"/>
+      <c r="BP7" s="118"/>
+      <c r="BQ7" s="118"/>
+      <c r="BR7" s="118"/>
+      <c r="BS7" s="118"/>
+      <c r="BT7" s="118"/>
+      <c r="BU7" s="118"/>
+      <c r="BV7" s="118"/>
+      <c r="BW7" s="118"/>
+      <c r="BX7" s="118" t="s">
         <v>300</v>
       </c>
-      <c r="BY7" s="122"/>
-      <c r="BZ7" s="122"/>
-      <c r="CA7" s="122"/>
-      <c r="CB7" s="122"/>
-      <c r="CC7" s="122"/>
-      <c r="CD7" s="122"/>
-      <c r="CE7" s="122"/>
-      <c r="CF7" s="122"/>
-      <c r="CG7" s="122"/>
-      <c r="CH7" s="122"/>
-      <c r="CI7" s="122"/>
-      <c r="CJ7" s="122"/>
-      <c r="CK7" s="122"/>
+      <c r="BY7" s="118"/>
+      <c r="BZ7" s="118"/>
+      <c r="CA7" s="118"/>
+      <c r="CB7" s="118"/>
+      <c r="CC7" s="118"/>
+      <c r="CD7" s="118"/>
+      <c r="CE7" s="118"/>
+      <c r="CF7" s="118"/>
+      <c r="CG7" s="118"/>
+      <c r="CH7" s="118"/>
+      <c r="CI7" s="118"/>
+      <c r="CJ7" s="118"/>
+      <c r="CK7" s="118"/>
       <c r="CL7" s="48" t="s">
         <v>370</v>
       </c>
@@ -29867,7 +29870,7 @@
         <v>405</v>
       </c>
       <c r="Y59" s="51" t="s">
-        <v>405</v>
+        <v>667</v>
       </c>
       <c r="Z59" s="51" t="s">
         <v>405</v>
@@ -30737,7 +30740,7 @@
         <v>405</v>
       </c>
       <c r="Y62" s="51" t="s">
-        <v>405</v>
+        <v>667</v>
       </c>
       <c r="Z62" s="51" t="s">
         <v>405</v>
@@ -31552,12 +31555,6 @@
   </sheetData>
   <autoFilter ref="A10:CZ58" xr:uid="{03E47C1A-8C76-40C7-A467-A5F175EC7551}"/>
   <mergeCells count="13">
-    <mergeCell ref="CS6:CZ6"/>
-    <mergeCell ref="CL6:CR6"/>
-    <mergeCell ref="AQ6:AU6"/>
-    <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="BJ7:BW7"/>
-    <mergeCell ref="BX7:CK7"/>
     <mergeCell ref="B2:H4"/>
     <mergeCell ref="T6:AA6"/>
     <mergeCell ref="AB6:AK6"/>
@@ -31565,6 +31562,12 @@
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="O6:P6"/>
+    <mergeCell ref="CS6:CZ6"/>
+    <mergeCell ref="CL6:CR6"/>
+    <mergeCell ref="AQ6:AU6"/>
+    <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="BJ7:BW7"/>
+    <mergeCell ref="BX7:CK7"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <conditionalFormatting sqref="T13:AZ13 BC13:CR13 BC16:CR16">

--- a/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
+++ b/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3453CA38-034A-458B-A531-E0C62F15A786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F14C94C-BF1D-4DB4-B71A-82E74ECCC904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
@@ -3489,13 +3489,13 @@
     <t>MG1CS022_6WZXSC_V037_L8-2_FFV_Hi_0x_BL013_MP0_VIN_IMMO_ON.hex</t>
   </si>
   <si>
-    <t>WF16424</t>
-  </si>
-  <si>
-    <t>WF16425</t>
-  </si>
-  <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>WF16437</t>
+  </si>
+  <si>
+    <t>WF16438</t>
   </si>
 </sst>
 </file>
@@ -4333,6 +4333,24 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4351,25 +4369,7 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12632,35 +12632,35 @@
     </row>
     <row r="2" spans="1:104">
       <c r="A2" s="39"/>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
     </row>
     <row r="3" spans="1:104" ht="4.5" customHeight="1">
       <c r="A3" s="39"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
     </row>
     <row r="4" spans="1:104" ht="4.5" customHeight="1">
       <c r="A4" s="39"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
     </row>
     <row r="5" spans="1:104" s="41" customFormat="1" ht="18.75" customHeight="1">
       <c r="C5" s="67"/>
@@ -12710,75 +12710,75 @@
       <c r="CZ5" s="67"/>
     </row>
     <row r="6" spans="1:104" ht="18" customHeight="1">
-      <c r="B6" s="122" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="121" t="s">
+      <c r="B6" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="115"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="114" t="s">
         <v>307</v>
       </c>
-      <c r="N6" s="121"/>
-      <c r="O6" s="121" t="s">
+      <c r="N6" s="114"/>
+      <c r="O6" s="114" t="s">
         <v>308</v>
       </c>
-      <c r="P6" s="121"/>
+      <c r="P6" s="114"/>
       <c r="Q6" s="60" t="s">
         <v>349</v>
       </c>
       <c r="R6" s="60"/>
       <c r="S6" s="60"/>
-      <c r="T6" s="120" t="s">
+      <c r="T6" s="111" t="s">
         <v>101</v>
       </c>
-      <c r="U6" s="120"/>
-      <c r="V6" s="120"/>
-      <c r="W6" s="120"/>
-      <c r="X6" s="120"/>
-      <c r="Y6" s="120"/>
-      <c r="Z6" s="120"/>
-      <c r="AA6" s="120"/>
-      <c r="AB6" s="116" t="s">
+      <c r="U6" s="111"/>
+      <c r="V6" s="111"/>
+      <c r="W6" s="111"/>
+      <c r="X6" s="111"/>
+      <c r="Y6" s="111"/>
+      <c r="Z6" s="111"/>
+      <c r="AA6" s="111"/>
+      <c r="AB6" s="112" t="s">
         <v>125</v>
       </c>
-      <c r="AC6" s="116"/>
-      <c r="AD6" s="116"/>
-      <c r="AE6" s="116"/>
-      <c r="AF6" s="116"/>
-      <c r="AG6" s="116"/>
-      <c r="AH6" s="116"/>
-      <c r="AI6" s="116"/>
-      <c r="AJ6" s="116"/>
-      <c r="AK6" s="116"/>
-      <c r="AL6" s="117" t="s">
+      <c r="AC6" s="112"/>
+      <c r="AD6" s="112"/>
+      <c r="AE6" s="112"/>
+      <c r="AF6" s="112"/>
+      <c r="AG6" s="112"/>
+      <c r="AH6" s="112"/>
+      <c r="AI6" s="112"/>
+      <c r="AJ6" s="112"/>
+      <c r="AK6" s="112"/>
+      <c r="AL6" s="113" t="s">
         <v>126</v>
       </c>
-      <c r="AM6" s="117"/>
-      <c r="AN6" s="117"/>
-      <c r="AO6" s="117"/>
-      <c r="AP6" s="117"/>
-      <c r="AQ6" s="116" t="s">
+      <c r="AM6" s="113"/>
+      <c r="AN6" s="113"/>
+      <c r="AO6" s="113"/>
+      <c r="AP6" s="113"/>
+      <c r="AQ6" s="112" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="116"/>
-      <c r="AS6" s="116"/>
-      <c r="AT6" s="116"/>
-      <c r="AU6" s="116"/>
-      <c r="AV6" s="117" t="s">
+      <c r="AR6" s="112"/>
+      <c r="AS6" s="112"/>
+      <c r="AT6" s="112"/>
+      <c r="AU6" s="112"/>
+      <c r="AV6" s="113" t="s">
         <v>165</v>
       </c>
-      <c r="AW6" s="117"/>
-      <c r="AX6" s="117"/>
-      <c r="AY6" s="117"/>
-      <c r="AZ6" s="117"/>
+      <c r="AW6" s="113"/>
+      <c r="AX6" s="113"/>
+      <c r="AY6" s="113"/>
+      <c r="AZ6" s="113"/>
       <c r="BA6" s="48"/>
       <c r="BB6" s="48"/>
       <c r="BC6" s="60" t="s">
@@ -12876,25 +12876,25 @@
       <c r="CK6" s="64">
         <v>14</v>
       </c>
-      <c r="CL6" s="113" t="s">
+      <c r="CL6" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="CM6" s="114"/>
-      <c r="CN6" s="114"/>
-      <c r="CO6" s="114"/>
-      <c r="CP6" s="114"/>
-      <c r="CQ6" s="114"/>
-      <c r="CR6" s="115"/>
-      <c r="CS6" s="110" t="s">
+      <c r="CM6" s="120"/>
+      <c r="CN6" s="120"/>
+      <c r="CO6" s="120"/>
+      <c r="CP6" s="120"/>
+      <c r="CQ6" s="120"/>
+      <c r="CR6" s="121"/>
+      <c r="CS6" s="116" t="s">
         <v>373</v>
       </c>
-      <c r="CT6" s="111"/>
-      <c r="CU6" s="111"/>
-      <c r="CV6" s="111"/>
-      <c r="CW6" s="111"/>
-      <c r="CX6" s="111"/>
-      <c r="CY6" s="111"/>
-      <c r="CZ6" s="112"/>
+      <c r="CT6" s="117"/>
+      <c r="CU6" s="117"/>
+      <c r="CV6" s="117"/>
+      <c r="CW6" s="117"/>
+      <c r="CX6" s="117"/>
+      <c r="CY6" s="117"/>
+      <c r="CZ6" s="118"/>
     </row>
     <row r="7" spans="1:104" ht="114" collapsed="1">
       <c r="A7" s="66" t="s">
@@ -13080,38 +13080,38 @@
       <c r="BI7" s="65" t="s">
         <v>340</v>
       </c>
-      <c r="BJ7" s="118" t="s">
+      <c r="BJ7" s="122" t="s">
         <v>299</v>
       </c>
-      <c r="BK7" s="118"/>
-      <c r="BL7" s="118"/>
-      <c r="BM7" s="118"/>
-      <c r="BN7" s="118"/>
-      <c r="BO7" s="118"/>
-      <c r="BP7" s="118"/>
-      <c r="BQ7" s="118"/>
-      <c r="BR7" s="118"/>
-      <c r="BS7" s="118"/>
-      <c r="BT7" s="118"/>
-      <c r="BU7" s="118"/>
-      <c r="BV7" s="118"/>
-      <c r="BW7" s="118"/>
-      <c r="BX7" s="118" t="s">
+      <c r="BK7" s="122"/>
+      <c r="BL7" s="122"/>
+      <c r="BM7" s="122"/>
+      <c r="BN7" s="122"/>
+      <c r="BO7" s="122"/>
+      <c r="BP7" s="122"/>
+      <c r="BQ7" s="122"/>
+      <c r="BR7" s="122"/>
+      <c r="BS7" s="122"/>
+      <c r="BT7" s="122"/>
+      <c r="BU7" s="122"/>
+      <c r="BV7" s="122"/>
+      <c r="BW7" s="122"/>
+      <c r="BX7" s="122" t="s">
         <v>300</v>
       </c>
-      <c r="BY7" s="118"/>
-      <c r="BZ7" s="118"/>
-      <c r="CA7" s="118"/>
-      <c r="CB7" s="118"/>
-      <c r="CC7" s="118"/>
-      <c r="CD7" s="118"/>
-      <c r="CE7" s="118"/>
-      <c r="CF7" s="118"/>
-      <c r="CG7" s="118"/>
-      <c r="CH7" s="118"/>
-      <c r="CI7" s="118"/>
-      <c r="CJ7" s="118"/>
-      <c r="CK7" s="118"/>
+      <c r="BY7" s="122"/>
+      <c r="BZ7" s="122"/>
+      <c r="CA7" s="122"/>
+      <c r="CB7" s="122"/>
+      <c r="CC7" s="122"/>
+      <c r="CD7" s="122"/>
+      <c r="CE7" s="122"/>
+      <c r="CF7" s="122"/>
+      <c r="CG7" s="122"/>
+      <c r="CH7" s="122"/>
+      <c r="CI7" s="122"/>
+      <c r="CJ7" s="122"/>
+      <c r="CK7" s="122"/>
       <c r="CL7" s="48" t="s">
         <v>370</v>
       </c>
@@ -29831,7 +29831,7 @@
         <v>661</v>
       </c>
       <c r="I59" s="78" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J59" s="53" t="s">
         <v>645</v>
@@ -29870,7 +29870,7 @@
         <v>405</v>
       </c>
       <c r="Y59" s="51" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="Z59" s="51" t="s">
         <v>405</v>
@@ -30701,7 +30701,7 @@
         <v>661</v>
       </c>
       <c r="I62" s="78" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="J62" s="53" t="s">
         <v>653</v>
@@ -30740,7 +30740,7 @@
         <v>405</v>
       </c>
       <c r="Y62" s="51" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="Z62" s="51" t="s">
         <v>405</v>
@@ -31555,6 +31555,12 @@
   </sheetData>
   <autoFilter ref="A10:CZ58" xr:uid="{03E47C1A-8C76-40C7-A467-A5F175EC7551}"/>
   <mergeCells count="13">
+    <mergeCell ref="CS6:CZ6"/>
+    <mergeCell ref="CL6:CR6"/>
+    <mergeCell ref="AQ6:AU6"/>
+    <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="BJ7:BW7"/>
+    <mergeCell ref="BX7:CK7"/>
     <mergeCell ref="B2:H4"/>
     <mergeCell ref="T6:AA6"/>
     <mergeCell ref="AB6:AK6"/>
@@ -31562,12 +31568,6 @@
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="O6:P6"/>
-    <mergeCell ref="CS6:CZ6"/>
-    <mergeCell ref="CL6:CR6"/>
-    <mergeCell ref="AQ6:AU6"/>
-    <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="BJ7:BW7"/>
-    <mergeCell ref="BX7:CK7"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <conditionalFormatting sqref="T13:AZ13 BC13:CR13 BC16:CR16">

--- a/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
+++ b/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F14C94C-BF1D-4DB4-B71A-82E74ECCC904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89F6166-B4C3-496C-95B3-9A80062EDB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkFlow_Detail" sheetId="4" r:id="rId1"/>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="669">
   <si>
     <t>HONDA 62XS CONTAINER</t>
   </si>
@@ -3480,9 +3480,6 @@
     <t>6WZX for MP0 event</t>
   </si>
   <si>
-    <t>MG1CS022_62XSC_V037</t>
-  </si>
-  <si>
     <t>MG1CS022_6WZXSC_V037_L8-2_FFV_Lo_0x_BL013_MP0_VIN_IMMO_ON.hex</t>
   </si>
   <si>
@@ -3496,6 +3493,12 @@
   </si>
   <si>
     <t>WF16438</t>
+  </si>
+  <si>
+    <t>MG1CS022_62XSC_V020_CS</t>
+  </si>
+  <si>
+    <t>V020</t>
   </si>
 </sst>
 </file>
@@ -4333,24 +4336,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4369,7 +4354,25 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12632,35 +12635,35 @@
     </row>
     <row r="2" spans="1:104">
       <c r="A2" s="39"/>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
     </row>
     <row r="3" spans="1:104" ht="4.5" customHeight="1">
       <c r="A3" s="39"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
     </row>
     <row r="4" spans="1:104" ht="4.5" customHeight="1">
       <c r="A4" s="39"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
     </row>
     <row r="5" spans="1:104" s="41" customFormat="1" ht="18.75" customHeight="1">
       <c r="C5" s="67"/>
@@ -12710,75 +12713,75 @@
       <c r="CZ5" s="67"/>
     </row>
     <row r="6" spans="1:104" ht="18" customHeight="1">
-      <c r="B6" s="115" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="114" t="s">
+      <c r="B6" s="122" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="121" t="s">
         <v>307</v>
       </c>
-      <c r="N6" s="114"/>
-      <c r="O6" s="114" t="s">
+      <c r="N6" s="121"/>
+      <c r="O6" s="121" t="s">
         <v>308</v>
       </c>
-      <c r="P6" s="114"/>
+      <c r="P6" s="121"/>
       <c r="Q6" s="60" t="s">
         <v>349</v>
       </c>
       <c r="R6" s="60"/>
       <c r="S6" s="60"/>
-      <c r="T6" s="111" t="s">
+      <c r="T6" s="120" t="s">
         <v>101</v>
       </c>
-      <c r="U6" s="111"/>
-      <c r="V6" s="111"/>
-      <c r="W6" s="111"/>
-      <c r="X6" s="111"/>
-      <c r="Y6" s="111"/>
-      <c r="Z6" s="111"/>
-      <c r="AA6" s="111"/>
-      <c r="AB6" s="112" t="s">
+      <c r="U6" s="120"/>
+      <c r="V6" s="120"/>
+      <c r="W6" s="120"/>
+      <c r="X6" s="120"/>
+      <c r="Y6" s="120"/>
+      <c r="Z6" s="120"/>
+      <c r="AA6" s="120"/>
+      <c r="AB6" s="116" t="s">
         <v>125</v>
       </c>
-      <c r="AC6" s="112"/>
-      <c r="AD6" s="112"/>
-      <c r="AE6" s="112"/>
-      <c r="AF6" s="112"/>
-      <c r="AG6" s="112"/>
-      <c r="AH6" s="112"/>
-      <c r="AI6" s="112"/>
-      <c r="AJ6" s="112"/>
-      <c r="AK6" s="112"/>
-      <c r="AL6" s="113" t="s">
+      <c r="AC6" s="116"/>
+      <c r="AD6" s="116"/>
+      <c r="AE6" s="116"/>
+      <c r="AF6" s="116"/>
+      <c r="AG6" s="116"/>
+      <c r="AH6" s="116"/>
+      <c r="AI6" s="116"/>
+      <c r="AJ6" s="116"/>
+      <c r="AK6" s="116"/>
+      <c r="AL6" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="AM6" s="113"/>
-      <c r="AN6" s="113"/>
-      <c r="AO6" s="113"/>
-      <c r="AP6" s="113"/>
-      <c r="AQ6" s="112" t="s">
+      <c r="AM6" s="117"/>
+      <c r="AN6" s="117"/>
+      <c r="AO6" s="117"/>
+      <c r="AP6" s="117"/>
+      <c r="AQ6" s="116" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="112"/>
-      <c r="AS6" s="112"/>
-      <c r="AT6" s="112"/>
-      <c r="AU6" s="112"/>
-      <c r="AV6" s="113" t="s">
+      <c r="AR6" s="116"/>
+      <c r="AS6" s="116"/>
+      <c r="AT6" s="116"/>
+      <c r="AU6" s="116"/>
+      <c r="AV6" s="117" t="s">
         <v>165</v>
       </c>
-      <c r="AW6" s="113"/>
-      <c r="AX6" s="113"/>
-      <c r="AY6" s="113"/>
-      <c r="AZ6" s="113"/>
+      <c r="AW6" s="117"/>
+      <c r="AX6" s="117"/>
+      <c r="AY6" s="117"/>
+      <c r="AZ6" s="117"/>
       <c r="BA6" s="48"/>
       <c r="BB6" s="48"/>
       <c r="BC6" s="60" t="s">
@@ -12876,25 +12879,25 @@
       <c r="CK6" s="64">
         <v>14</v>
       </c>
-      <c r="CL6" s="119" t="s">
+      <c r="CL6" s="113" t="s">
         <v>193</v>
       </c>
-      <c r="CM6" s="120"/>
-      <c r="CN6" s="120"/>
-      <c r="CO6" s="120"/>
-      <c r="CP6" s="120"/>
-      <c r="CQ6" s="120"/>
-      <c r="CR6" s="121"/>
-      <c r="CS6" s="116" t="s">
+      <c r="CM6" s="114"/>
+      <c r="CN6" s="114"/>
+      <c r="CO6" s="114"/>
+      <c r="CP6" s="114"/>
+      <c r="CQ6" s="114"/>
+      <c r="CR6" s="115"/>
+      <c r="CS6" s="110" t="s">
         <v>373</v>
       </c>
-      <c r="CT6" s="117"/>
-      <c r="CU6" s="117"/>
-      <c r="CV6" s="117"/>
-      <c r="CW6" s="117"/>
-      <c r="CX6" s="117"/>
-      <c r="CY6" s="117"/>
-      <c r="CZ6" s="118"/>
+      <c r="CT6" s="111"/>
+      <c r="CU6" s="111"/>
+      <c r="CV6" s="111"/>
+      <c r="CW6" s="111"/>
+      <c r="CX6" s="111"/>
+      <c r="CY6" s="111"/>
+      <c r="CZ6" s="112"/>
     </row>
     <row r="7" spans="1:104" ht="114" collapsed="1">
       <c r="A7" s="66" t="s">
@@ -13080,38 +13083,38 @@
       <c r="BI7" s="65" t="s">
         <v>340</v>
       </c>
-      <c r="BJ7" s="122" t="s">
+      <c r="BJ7" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="BK7" s="122"/>
-      <c r="BL7" s="122"/>
-      <c r="BM7" s="122"/>
-      <c r="BN7" s="122"/>
-      <c r="BO7" s="122"/>
-      <c r="BP7" s="122"/>
-      <c r="BQ7" s="122"/>
-      <c r="BR7" s="122"/>
-      <c r="BS7" s="122"/>
-      <c r="BT7" s="122"/>
-      <c r="BU7" s="122"/>
-      <c r="BV7" s="122"/>
-      <c r="BW7" s="122"/>
-      <c r="BX7" s="122" t="s">
+      <c r="BK7" s="118"/>
+      <c r="BL7" s="118"/>
+      <c r="BM7" s="118"/>
+      <c r="BN7" s="118"/>
+      <c r="BO7" s="118"/>
+      <c r="BP7" s="118"/>
+      <c r="BQ7" s="118"/>
+      <c r="BR7" s="118"/>
+      <c r="BS7" s="118"/>
+      <c r="BT7" s="118"/>
+      <c r="BU7" s="118"/>
+      <c r="BV7" s="118"/>
+      <c r="BW7" s="118"/>
+      <c r="BX7" s="118" t="s">
         <v>300</v>
       </c>
-      <c r="BY7" s="122"/>
-      <c r="BZ7" s="122"/>
-      <c r="CA7" s="122"/>
-      <c r="CB7" s="122"/>
-      <c r="CC7" s="122"/>
-      <c r="CD7" s="122"/>
-      <c r="CE7" s="122"/>
-      <c r="CF7" s="122"/>
-      <c r="CG7" s="122"/>
-      <c r="CH7" s="122"/>
-      <c r="CI7" s="122"/>
-      <c r="CJ7" s="122"/>
-      <c r="CK7" s="122"/>
+      <c r="BY7" s="118"/>
+      <c r="BZ7" s="118"/>
+      <c r="CA7" s="118"/>
+      <c r="CB7" s="118"/>
+      <c r="CC7" s="118"/>
+      <c r="CD7" s="118"/>
+      <c r="CE7" s="118"/>
+      <c r="CF7" s="118"/>
+      <c r="CG7" s="118"/>
+      <c r="CH7" s="118"/>
+      <c r="CI7" s="118"/>
+      <c r="CJ7" s="118"/>
+      <c r="CK7" s="118"/>
       <c r="CL7" s="48" t="s">
         <v>370</v>
       </c>
@@ -29831,7 +29834,7 @@
         <v>661</v>
       </c>
       <c r="I59" s="78" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="J59" s="53" t="s">
         <v>645</v>
@@ -29870,7 +29873,7 @@
         <v>405</v>
       </c>
       <c r="Y59" s="51" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="Z59" s="51" t="s">
         <v>405</v>
@@ -29951,10 +29954,10 @@
         <v>0</v>
       </c>
       <c r="AY59" s="51" t="s">
+        <v>667</v>
+      </c>
+      <c r="AZ59" s="51" t="s">
         <v>662</v>
-      </c>
-      <c r="AZ59" s="51" t="s">
-        <v>663</v>
       </c>
       <c r="BA59" s="51"/>
       <c r="BB59" s="51"/>
@@ -29969,7 +29972,7 @@
         <v>646</v>
       </c>
       <c r="BF59" s="51" t="s">
-        <v>542</v>
+        <v>668</v>
       </c>
       <c r="BG59" s="51" t="s">
         <v>467</v>
@@ -30701,7 +30704,7 @@
         <v>661</v>
       </c>
       <c r="I62" s="78" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J62" s="53" t="s">
         <v>653</v>
@@ -30740,7 +30743,7 @@
         <v>405</v>
       </c>
       <c r="Y62" s="51" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="Z62" s="51" t="s">
         <v>405</v>
@@ -30821,10 +30824,10 @@
         <v>0</v>
       </c>
       <c r="AY62" s="51" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="AZ62" s="51" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="BA62" s="51"/>
       <c r="BB62" s="51"/>
@@ -30839,7 +30842,7 @@
         <v>646</v>
       </c>
       <c r="BF62" s="51" t="s">
-        <v>542</v>
+        <v>668</v>
       </c>
       <c r="BG62" s="51" t="s">
         <v>467</v>
@@ -31555,12 +31558,6 @@
   </sheetData>
   <autoFilter ref="A10:CZ58" xr:uid="{03E47C1A-8C76-40C7-A467-A5F175EC7551}"/>
   <mergeCells count="13">
-    <mergeCell ref="CS6:CZ6"/>
-    <mergeCell ref="CL6:CR6"/>
-    <mergeCell ref="AQ6:AU6"/>
-    <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="BJ7:BW7"/>
-    <mergeCell ref="BX7:CK7"/>
     <mergeCell ref="B2:H4"/>
     <mergeCell ref="T6:AA6"/>
     <mergeCell ref="AB6:AK6"/>
@@ -31568,6 +31565,12 @@
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="O6:P6"/>
+    <mergeCell ref="CS6:CZ6"/>
+    <mergeCell ref="CL6:CR6"/>
+    <mergeCell ref="AQ6:AU6"/>
+    <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="BJ7:BW7"/>
+    <mergeCell ref="BX7:CK7"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <conditionalFormatting sqref="T13:AZ13 BC13:CR13 BC16:CR16">

--- a/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
+++ b/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89F6166-B4C3-496C-95B3-9A80062EDB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28FE905-461A-438C-B323-263B68BAFCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
@@ -3489,16 +3489,16 @@
     <t>No</t>
   </si>
   <si>
-    <t>WF16437</t>
-  </si>
-  <si>
-    <t>WF16438</t>
-  </si>
-  <si>
     <t>MG1CS022_62XSC_V020_CS</t>
   </si>
   <si>
     <t>V020</t>
+  </si>
+  <si>
+    <t>WF16443</t>
+  </si>
+  <si>
+    <t>WF16444</t>
   </si>
 </sst>
 </file>
@@ -29834,7 +29834,7 @@
         <v>661</v>
       </c>
       <c r="I59" s="78" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="J59" s="53" t="s">
         <v>645</v>
@@ -29954,7 +29954,7 @@
         <v>0</v>
       </c>
       <c r="AY59" s="51" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AZ59" s="51" t="s">
         <v>662</v>
@@ -29972,7 +29972,7 @@
         <v>646</v>
       </c>
       <c r="BF59" s="51" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="BG59" s="51" t="s">
         <v>467</v>
@@ -30704,7 +30704,7 @@
         <v>661</v>
       </c>
       <c r="I62" s="78" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="J62" s="53" t="s">
         <v>653</v>
@@ -30824,7 +30824,7 @@
         <v>0</v>
       </c>
       <c r="AY62" s="51" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AZ62" s="51" t="s">
         <v>663</v>
@@ -30842,7 +30842,7 @@
         <v>646</v>
       </c>
       <c r="BF62" s="51" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="BG62" s="51" t="s">
         <v>467</v>

--- a/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
+++ b/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28FE905-461A-438C-B323-263B68BAFCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD60552-2684-46E1-95C9-35764DE67030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3139" uniqueCount="673">
   <si>
     <t>HONDA 62XS CONTAINER</t>
   </si>
@@ -3495,10 +3495,22 @@
     <t>V020</t>
   </si>
   <si>
-    <t>WF16443</t>
-  </si>
-  <si>
-    <t>WF16444</t>
+    <t>WF16447</t>
+  </si>
+  <si>
+    <t>WF16448</t>
+  </si>
+  <si>
+    <t>10SW072941</t>
+  </si>
+  <si>
+    <t>3E10174613</t>
+  </si>
+  <si>
+    <t>10SW072942</t>
+  </si>
+  <si>
+    <t>3E10174614</t>
   </si>
 </sst>
 </file>
@@ -4053,7 +4065,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4336,6 +4348,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="19" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -12635,35 +12650,35 @@
     </row>
     <row r="2" spans="1:104">
       <c r="A2" s="39"/>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
     </row>
     <row r="3" spans="1:104" ht="4.5" customHeight="1">
       <c r="A3" s="39"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
     </row>
     <row r="4" spans="1:104" ht="4.5" customHeight="1">
       <c r="A4" s="39"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
     </row>
     <row r="5" spans="1:104" s="41" customFormat="1" ht="18.75" customHeight="1">
       <c r="C5" s="67"/>
@@ -12713,75 +12728,75 @@
       <c r="CZ5" s="67"/>
     </row>
     <row r="6" spans="1:104" ht="18" customHeight="1">
-      <c r="B6" s="122" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="121" t="s">
+      <c r="B6" s="123" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="123"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="123"/>
+      <c r="M6" s="122" t="s">
         <v>307</v>
       </c>
-      <c r="N6" s="121"/>
-      <c r="O6" s="121" t="s">
+      <c r="N6" s="122"/>
+      <c r="O6" s="122" t="s">
         <v>308</v>
       </c>
-      <c r="P6" s="121"/>
+      <c r="P6" s="122"/>
       <c r="Q6" s="60" t="s">
         <v>349</v>
       </c>
       <c r="R6" s="60"/>
       <c r="S6" s="60"/>
-      <c r="T6" s="120" t="s">
+      <c r="T6" s="121" t="s">
         <v>101</v>
       </c>
-      <c r="U6" s="120"/>
-      <c r="V6" s="120"/>
-      <c r="W6" s="120"/>
-      <c r="X6" s="120"/>
-      <c r="Y6" s="120"/>
-      <c r="Z6" s="120"/>
-      <c r="AA6" s="120"/>
-      <c r="AB6" s="116" t="s">
+      <c r="U6" s="121"/>
+      <c r="V6" s="121"/>
+      <c r="W6" s="121"/>
+      <c r="X6" s="121"/>
+      <c r="Y6" s="121"/>
+      <c r="Z6" s="121"/>
+      <c r="AA6" s="121"/>
+      <c r="AB6" s="117" t="s">
         <v>125</v>
       </c>
-      <c r="AC6" s="116"/>
-      <c r="AD6" s="116"/>
-      <c r="AE6" s="116"/>
-      <c r="AF6" s="116"/>
-      <c r="AG6" s="116"/>
-      <c r="AH6" s="116"/>
-      <c r="AI6" s="116"/>
-      <c r="AJ6" s="116"/>
-      <c r="AK6" s="116"/>
-      <c r="AL6" s="117" t="s">
+      <c r="AC6" s="117"/>
+      <c r="AD6" s="117"/>
+      <c r="AE6" s="117"/>
+      <c r="AF6" s="117"/>
+      <c r="AG6" s="117"/>
+      <c r="AH6" s="117"/>
+      <c r="AI6" s="117"/>
+      <c r="AJ6" s="117"/>
+      <c r="AK6" s="117"/>
+      <c r="AL6" s="118" t="s">
         <v>126</v>
       </c>
-      <c r="AM6" s="117"/>
-      <c r="AN6" s="117"/>
-      <c r="AO6" s="117"/>
-      <c r="AP6" s="117"/>
-      <c r="AQ6" s="116" t="s">
+      <c r="AM6" s="118"/>
+      <c r="AN6" s="118"/>
+      <c r="AO6" s="118"/>
+      <c r="AP6" s="118"/>
+      <c r="AQ6" s="117" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="116"/>
-      <c r="AS6" s="116"/>
-      <c r="AT6" s="116"/>
-      <c r="AU6" s="116"/>
-      <c r="AV6" s="117" t="s">
+      <c r="AR6" s="117"/>
+      <c r="AS6" s="117"/>
+      <c r="AT6" s="117"/>
+      <c r="AU6" s="117"/>
+      <c r="AV6" s="118" t="s">
         <v>165</v>
       </c>
-      <c r="AW6" s="117"/>
-      <c r="AX6" s="117"/>
-      <c r="AY6" s="117"/>
-      <c r="AZ6" s="117"/>
+      <c r="AW6" s="118"/>
+      <c r="AX6" s="118"/>
+      <c r="AY6" s="118"/>
+      <c r="AZ6" s="118"/>
       <c r="BA6" s="48"/>
       <c r="BB6" s="48"/>
       <c r="BC6" s="60" t="s">
@@ -12879,25 +12894,25 @@
       <c r="CK6" s="64">
         <v>14</v>
       </c>
-      <c r="CL6" s="113" t="s">
+      <c r="CL6" s="114" t="s">
         <v>193</v>
       </c>
-      <c r="CM6" s="114"/>
-      <c r="CN6" s="114"/>
-      <c r="CO6" s="114"/>
-      <c r="CP6" s="114"/>
-      <c r="CQ6" s="114"/>
-      <c r="CR6" s="115"/>
-      <c r="CS6" s="110" t="s">
+      <c r="CM6" s="115"/>
+      <c r="CN6" s="115"/>
+      <c r="CO6" s="115"/>
+      <c r="CP6" s="115"/>
+      <c r="CQ6" s="115"/>
+      <c r="CR6" s="116"/>
+      <c r="CS6" s="111" t="s">
         <v>373</v>
       </c>
-      <c r="CT6" s="111"/>
-      <c r="CU6" s="111"/>
-      <c r="CV6" s="111"/>
-      <c r="CW6" s="111"/>
-      <c r="CX6" s="111"/>
-      <c r="CY6" s="111"/>
-      <c r="CZ6" s="112"/>
+      <c r="CT6" s="112"/>
+      <c r="CU6" s="112"/>
+      <c r="CV6" s="112"/>
+      <c r="CW6" s="112"/>
+      <c r="CX6" s="112"/>
+      <c r="CY6" s="112"/>
+      <c r="CZ6" s="113"/>
     </row>
     <row r="7" spans="1:104" ht="114" collapsed="1">
       <c r="A7" s="66" t="s">
@@ -13083,38 +13098,38 @@
       <c r="BI7" s="65" t="s">
         <v>340</v>
       </c>
-      <c r="BJ7" s="118" t="s">
+      <c r="BJ7" s="119" t="s">
         <v>299</v>
       </c>
-      <c r="BK7" s="118"/>
-      <c r="BL7" s="118"/>
-      <c r="BM7" s="118"/>
-      <c r="BN7" s="118"/>
-      <c r="BO7" s="118"/>
-      <c r="BP7" s="118"/>
-      <c r="BQ7" s="118"/>
-      <c r="BR7" s="118"/>
-      <c r="BS7" s="118"/>
-      <c r="BT7" s="118"/>
-      <c r="BU7" s="118"/>
-      <c r="BV7" s="118"/>
-      <c r="BW7" s="118"/>
-      <c r="BX7" s="118" t="s">
+      <c r="BK7" s="119"/>
+      <c r="BL7" s="119"/>
+      <c r="BM7" s="119"/>
+      <c r="BN7" s="119"/>
+      <c r="BO7" s="119"/>
+      <c r="BP7" s="119"/>
+      <c r="BQ7" s="119"/>
+      <c r="BR7" s="119"/>
+      <c r="BS7" s="119"/>
+      <c r="BT7" s="119"/>
+      <c r="BU7" s="119"/>
+      <c r="BV7" s="119"/>
+      <c r="BW7" s="119"/>
+      <c r="BX7" s="119" t="s">
         <v>300</v>
       </c>
-      <c r="BY7" s="118"/>
-      <c r="BZ7" s="118"/>
-      <c r="CA7" s="118"/>
-      <c r="CB7" s="118"/>
-      <c r="CC7" s="118"/>
-      <c r="CD7" s="118"/>
-      <c r="CE7" s="118"/>
-      <c r="CF7" s="118"/>
-      <c r="CG7" s="118"/>
-      <c r="CH7" s="118"/>
-      <c r="CI7" s="118"/>
-      <c r="CJ7" s="118"/>
-      <c r="CK7" s="118"/>
+      <c r="BY7" s="119"/>
+      <c r="BZ7" s="119"/>
+      <c r="CA7" s="119"/>
+      <c r="CB7" s="119"/>
+      <c r="CC7" s="119"/>
+      <c r="CD7" s="119"/>
+      <c r="CE7" s="119"/>
+      <c r="CF7" s="119"/>
+      <c r="CG7" s="119"/>
+      <c r="CH7" s="119"/>
+      <c r="CI7" s="119"/>
+      <c r="CJ7" s="119"/>
+      <c r="CK7" s="119"/>
       <c r="CL7" s="48" t="s">
         <v>370</v>
       </c>
@@ -29839,7 +29854,9 @@
       <c r="J59" s="53" t="s">
         <v>645</v>
       </c>
-      <c r="K59" s="53"/>
+      <c r="K59" s="110" t="s">
+        <v>669</v>
+      </c>
       <c r="L59" s="51"/>
       <c r="M59" s="51"/>
       <c r="N59" s="51"/>
@@ -29935,9 +29952,9 @@
         <f>LEFT((SUBSTITUTE(J59," ","")),LEN(SUBSTITUTE(J59," ",""))-4)</f>
         <v>37820-6WZ-M61</v>
       </c>
-      <c r="AS59" s="54">
+      <c r="AS59" s="54" t="str">
         <f>K59</f>
-        <v>0</v>
+        <v>10SW072941</v>
       </c>
       <c r="AT59" s="51" t="s">
         <v>660</v>
@@ -29948,10 +29965,12 @@
       <c r="AV59" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW59" s="77"/>
-      <c r="AX59" s="54">
+      <c r="AW59" s="77" t="s">
+        <v>670</v>
+      </c>
+      <c r="AX59" s="54" t="str">
         <f>K59</f>
-        <v>0</v>
+        <v>10SW072941</v>
       </c>
       <c r="AY59" s="51" t="s">
         <v>665</v>
@@ -30488,7 +30507,7 @@
       </c>
       <c r="AS61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT61" s="47" t="b">
         <f t="shared" si="350"/>
@@ -30504,11 +30523,11 @@
       </c>
       <c r="AW61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX61" s="47" t="b">
         <f t="shared" si="350"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY61" s="47" t="b">
         <f t="shared" si="350"/>
@@ -30709,7 +30728,9 @@
       <c r="J62" s="53" t="s">
         <v>653</v>
       </c>
-      <c r="K62" s="53"/>
+      <c r="K62" s="110" t="s">
+        <v>671</v>
+      </c>
       <c r="L62" s="51"/>
       <c r="M62" s="51"/>
       <c r="N62" s="51"/>
@@ -30805,9 +30826,9 @@
         <f>LEFT((SUBSTITUTE(J62," ","")),LEN(SUBSTITUTE(J62," ",""))-4)</f>
         <v>37820-6WZ-M71</v>
       </c>
-      <c r="AS62" s="54">
+      <c r="AS62" s="54" t="str">
         <f>K62</f>
-        <v>0</v>
+        <v>10SW072942</v>
       </c>
       <c r="AT62" s="51" t="s">
         <v>660</v>
@@ -30818,10 +30839,12 @@
       <c r="AV62" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="AW62" s="77"/>
-      <c r="AX62" s="54">
+      <c r="AW62" s="77" t="s">
+        <v>672</v>
+      </c>
+      <c r="AX62" s="54" t="str">
         <f>K62</f>
-        <v>0</v>
+        <v>10SW072942</v>
       </c>
       <c r="AY62" s="51" t="s">
         <v>665</v>
@@ -31358,7 +31381,7 @@
       </c>
       <c r="AS64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT64" s="47" t="b">
         <f t="shared" si="367"/>
@@ -31374,11 +31397,11 @@
       </c>
       <c r="AW64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX64" s="47" t="b">
         <f t="shared" si="367"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY64" s="47" t="b">
         <f t="shared" si="367"/>

--- a/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
+++ b/datas/mastersheet/Honda_62XS_Container_MasterSheet_r02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD60552-2684-46E1-95C9-35764DE67030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74430C25-0759-401E-8D93-086446544D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
@@ -3495,22 +3495,22 @@
     <t>V020</t>
   </si>
   <si>
-    <t>WF16447</t>
-  </si>
-  <si>
     <t>WF16448</t>
   </si>
   <si>
-    <t>10SW072941</t>
-  </si>
-  <si>
-    <t>3E10174613</t>
-  </si>
-  <si>
     <t>10SW072942</t>
   </si>
   <si>
     <t>3E10174614</t>
+  </si>
+  <si>
+    <t>WF16449</t>
+  </si>
+  <si>
+    <t>10SW072943</t>
+  </si>
+  <si>
+    <t>3E10174615</t>
   </si>
 </sst>
 </file>
@@ -29849,13 +29849,13 @@
         <v>661</v>
       </c>
       <c r="I59" s="78" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="J59" s="53" t="s">
         <v>645</v>
       </c>
       <c r="K59" s="110" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L59" s="51"/>
       <c r="M59" s="51"/>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AS59" s="54" t="str">
         <f>K59</f>
-        <v>10SW072941</v>
+        <v>10SW072943</v>
       </c>
       <c r="AT59" s="51" t="s">
         <v>660</v>
@@ -29966,11 +29966,11 @@
         <v>423</v>
       </c>
       <c r="AW59" s="77" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AX59" s="54" t="str">
         <f>K59</f>
-        <v>10SW072941</v>
+        <v>10SW072943</v>
       </c>
       <c r="AY59" s="51" t="s">
         <v>665</v>
@@ -30723,13 +30723,13 @@
         <v>661</v>
       </c>
       <c r="I62" s="78" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J62" s="53" t="s">
         <v>653</v>
       </c>
       <c r="K62" s="110" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="L62" s="51"/>
       <c r="M62" s="51"/>
@@ -30840,7 +30840,7 @@
         <v>423</v>
       </c>
       <c r="AW62" s="77" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="AX62" s="54" t="str">
         <f>K62</f>
